--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T432"/>
+  <dimension ref="A1:T433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28866,6 +28866,72 @@
         <v>267.61</v>
       </c>
       <c r="T432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="C433" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="D433" t="n">
+        <v>302.55</v>
+      </c>
+      <c r="E433" t="n">
+        <v>300.81</v>
+      </c>
+      <c r="F433" t="n">
+        <v>298.53</v>
+      </c>
+      <c r="G433" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="H433" t="n">
+        <v>294.53</v>
+      </c>
+      <c r="I433" t="n">
+        <v>301.29</v>
+      </c>
+      <c r="J433" t="n">
+        <v>295.32</v>
+      </c>
+      <c r="K433" t="n">
+        <v>289.63</v>
+      </c>
+      <c r="L433" t="n">
+        <v>280.61</v>
+      </c>
+      <c r="M433" t="n">
+        <v>273.71</v>
+      </c>
+      <c r="N433" t="n">
+        <v>259.96</v>
+      </c>
+      <c r="O433" t="n">
+        <v>269.85</v>
+      </c>
+      <c r="P433" t="n">
+        <v>272.07</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="R433" t="n">
+        <v>271.03</v>
+      </c>
+      <c r="S433" t="n">
+        <v>267.3</v>
+      </c>
+      <c r="T433" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28882,7 +28948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B507"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33955,6 +34021,26 @@
       </c>
       <c r="B507" t="n">
         <v>1.05</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>-0.16</v>
       </c>
     </row>
   </sheetData>
@@ -34123,28 +34209,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6743620279516052</v>
+        <v>-0.6689866442843282</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K2" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08153426006239817</v>
+        <v>0.08059702486316989</v>
       </c>
       <c r="M2" t="n">
-        <v>14.58747747507032</v>
+        <v>14.58265634452935</v>
       </c>
       <c r="N2" t="n">
-        <v>308.2252060836601</v>
+        <v>307.8778960091722</v>
       </c>
       <c r="O2" t="n">
-        <v>17.55634375613727</v>
+        <v>17.54644966963893</v>
       </c>
       <c r="P2" t="n">
-        <v>310.7091539371564</v>
+        <v>310.6562218940967</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34201,28 +34287,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6762178026504737</v>
+        <v>-0.6699049983197874</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K3" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1030258678115858</v>
+        <v>0.1015281675306614</v>
       </c>
       <c r="M3" t="n">
-        <v>12.92452138864543</v>
+        <v>12.92854573849527</v>
       </c>
       <c r="N3" t="n">
-        <v>246.0603349831714</v>
+        <v>246.0202197996028</v>
       </c>
       <c r="O3" t="n">
-        <v>15.68631043244942</v>
+        <v>15.68503171178187</v>
       </c>
       <c r="P3" t="n">
-        <v>304.0886277947694</v>
+        <v>304.0278576079164</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34279,28 +34365,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9604494704312805</v>
+        <v>-0.9503813048408076</v>
       </c>
       <c r="J4" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1426034489210919</v>
+        <v>0.1401229569261588</v>
       </c>
       <c r="M4" t="n">
-        <v>11.10265868142304</v>
+        <v>11.1232206736616</v>
       </c>
       <c r="N4" t="n">
-        <v>342.0601807833538</v>
+        <v>342.6251527184708</v>
       </c>
       <c r="O4" t="n">
-        <v>18.49486903936748</v>
+        <v>18.51013648567916</v>
       </c>
       <c r="P4" t="n">
-        <v>303.5031225443919</v>
+        <v>303.4061580203916</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34357,28 +34443,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.192648048431783</v>
+        <v>-1.180777825843714</v>
       </c>
       <c r="J5" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K5" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3005926393461142</v>
+        <v>0.2954630388295173</v>
       </c>
       <c r="M5" t="n">
-        <v>11.19382505267572</v>
+        <v>11.22348585970524</v>
       </c>
       <c r="N5" t="n">
-        <v>200.7015315314814</v>
+        <v>202.0740314092019</v>
       </c>
       <c r="O5" t="n">
-        <v>14.16691679694214</v>
+        <v>14.2152745808585</v>
       </c>
       <c r="P5" t="n">
-        <v>303.9839891948546</v>
+        <v>303.8679346079061</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34435,28 +34521,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.227133041356751</v>
+        <v>-1.215895482482945</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K6" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2843904117179012</v>
+        <v>0.2801330022700623</v>
       </c>
       <c r="M6" t="n">
-        <v>12.26572327982358</v>
+        <v>12.30298385107953</v>
       </c>
       <c r="N6" t="n">
-        <v>233.6933078544344</v>
+        <v>234.8426053258161</v>
       </c>
       <c r="O6" t="n">
-        <v>15.28703070757805</v>
+        <v>15.32457520865802</v>
       </c>
       <c r="P6" t="n">
-        <v>303.6641017181673</v>
+        <v>303.5558749972881</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34513,28 +34599,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.314092246167343</v>
+        <v>-1.299221341866313</v>
       </c>
       <c r="J7" t="n">
+        <v>432</v>
+      </c>
+      <c r="K7" t="n">
         <v>431</v>
       </c>
-      <c r="K7" t="n">
-        <v>430</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.274252392883393</v>
+        <v>0.2685917733068616</v>
       </c>
       <c r="M7" t="n">
-        <v>13.38315775148017</v>
+        <v>13.4414380899805</v>
       </c>
       <c r="N7" t="n">
-        <v>282.4862585674047</v>
+        <v>284.7975381088353</v>
       </c>
       <c r="O7" t="n">
-        <v>16.80732752603473</v>
+        <v>16.87594554710448</v>
       </c>
       <c r="P7" t="n">
-        <v>301.1764542418014</v>
+        <v>301.0334294130026</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34591,28 +34677,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.43883692210895</v>
+        <v>-1.426053506666061</v>
       </c>
       <c r="J8" t="n">
+        <v>432</v>
+      </c>
+      <c r="K8" t="n">
         <v>431</v>
       </c>
-      <c r="K8" t="n">
-        <v>430</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2479473588040788</v>
+        <v>0.2444425848506215</v>
       </c>
       <c r="M8" t="n">
-        <v>15.06509852197437</v>
+        <v>15.10052739672341</v>
       </c>
       <c r="N8" t="n">
-        <v>388.1703292505092</v>
+        <v>389.4619652383766</v>
       </c>
       <c r="O8" t="n">
-        <v>19.70203870797409</v>
+        <v>19.73479073206444</v>
       </c>
       <c r="P8" t="n">
-        <v>301.5039280130793</v>
+        <v>301.3809801567706</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34669,28 +34755,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.040696079399576</v>
+        <v>-1.025633704312289</v>
       </c>
       <c r="J9" t="n">
+        <v>432</v>
+      </c>
+      <c r="K9" t="n">
         <v>431</v>
       </c>
-      <c r="K9" t="n">
-        <v>430</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1503245837125391</v>
+        <v>0.1462105323562185</v>
       </c>
       <c r="M9" t="n">
-        <v>15.51587430092607</v>
+        <v>15.56330104780229</v>
       </c>
       <c r="N9" t="n">
-        <v>378.4263022295104</v>
+        <v>380.5918705560495</v>
       </c>
       <c r="O9" t="n">
-        <v>19.45318231625639</v>
+        <v>19.50876394229141</v>
       </c>
       <c r="P9" t="n">
-        <v>292.2950420833052</v>
+        <v>292.150175733919</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34747,28 +34833,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.046969547602786</v>
+        <v>-1.034458221874244</v>
       </c>
       <c r="J10" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K10" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1947323150627448</v>
+        <v>0.1905457557842207</v>
       </c>
       <c r="M10" t="n">
-        <v>13.31033798242729</v>
+        <v>13.34678093812722</v>
       </c>
       <c r="N10" t="n">
-        <v>282.533735678329</v>
+        <v>283.9892642515168</v>
       </c>
       <c r="O10" t="n">
-        <v>16.808739859916</v>
+        <v>16.85198101860778</v>
       </c>
       <c r="P10" t="n">
-        <v>292.6666147135433</v>
+        <v>292.5468280497141</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34825,28 +34911,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.111429253805495</v>
+        <v>-1.098138711786983</v>
       </c>
       <c r="J11" t="n">
+        <v>432</v>
+      </c>
+      <c r="K11" t="n">
         <v>431</v>
       </c>
-      <c r="K11" t="n">
-        <v>430</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1955373104279122</v>
+        <v>0.191331540754785</v>
       </c>
       <c r="M11" t="n">
-        <v>13.99936694966294</v>
+        <v>14.03306837641515</v>
       </c>
       <c r="N11" t="n">
-        <v>313.9767156647189</v>
+        <v>315.6113479470293</v>
       </c>
       <c r="O11" t="n">
-        <v>17.71938812895973</v>
+        <v>17.76545377824696</v>
       </c>
       <c r="P11" t="n">
-        <v>286.8140816740679</v>
+        <v>286.6862723143705</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34903,28 +34989,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8128115877528878</v>
+        <v>-0.802416848935173</v>
       </c>
       <c r="J12" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K12" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08302258367626481</v>
+        <v>0.08118930830690385</v>
       </c>
       <c r="M12" t="n">
-        <v>16.91575700850128</v>
+        <v>16.93020478955631</v>
       </c>
       <c r="N12" t="n">
-        <v>442.4167119469898</v>
+        <v>442.7979704773992</v>
       </c>
       <c r="O12" t="n">
-        <v>21.03370418987083</v>
+        <v>21.04276527639367</v>
       </c>
       <c r="P12" t="n">
-        <v>277.2881507286075</v>
+        <v>277.1863274841362</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34981,28 +35067,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6264567221148137</v>
+        <v>-0.6202017414845357</v>
       </c>
       <c r="J13" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K13" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04845787246075473</v>
+        <v>0.04770154810276805</v>
       </c>
       <c r="M13" t="n">
-        <v>17.76656263651064</v>
+        <v>17.75783462259304</v>
       </c>
       <c r="N13" t="n">
-        <v>480.6692683029983</v>
+        <v>480.0668224922285</v>
       </c>
       <c r="O13" t="n">
-        <v>21.92417086922555</v>
+        <v>21.91042725489917</v>
       </c>
       <c r="P13" t="n">
-        <v>275.1529421766385</v>
+        <v>275.0931709526754</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35059,28 +35145,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.440182811188594</v>
+        <v>-1.434850069312458</v>
       </c>
       <c r="J14" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K14" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2292352913837926</v>
+        <v>0.2285801034287744</v>
       </c>
       <c r="M14" t="n">
-        <v>16.35305540365893</v>
+        <v>16.34431352744853</v>
       </c>
       <c r="N14" t="n">
-        <v>432.8068508227597</v>
+        <v>432.1819453945802</v>
       </c>
       <c r="O14" t="n">
-        <v>20.80401045045786</v>
+        <v>20.7889861560053</v>
       </c>
       <c r="P14" t="n">
-        <v>284.9327711717132</v>
+        <v>284.8815517932435</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35137,28 +35223,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4297854389698629</v>
+        <v>-0.424063698978707</v>
       </c>
       <c r="J15" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K15" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04007531680952592</v>
+        <v>0.03917126700422491</v>
       </c>
       <c r="M15" t="n">
-        <v>12.95238418308544</v>
+        <v>12.95869419119415</v>
       </c>
       <c r="N15" t="n">
-        <v>270.18764526118</v>
+        <v>269.9795054216642</v>
       </c>
       <c r="O15" t="n">
-        <v>16.43738559690014</v>
+        <v>16.43105308316129</v>
       </c>
       <c r="P15" t="n">
-        <v>267.6000063681472</v>
+        <v>267.5442204956163</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35215,28 +35301,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.011825868122979</v>
+        <v>-1.004670573469824</v>
       </c>
       <c r="J16" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K16" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2315430822721649</v>
+        <v>0.2292714600951018</v>
       </c>
       <c r="M16" t="n">
-        <v>10.9397686105092</v>
+        <v>10.9648518223272</v>
       </c>
       <c r="N16" t="n">
-        <v>209.3781323675049</v>
+        <v>209.5695199931692</v>
       </c>
       <c r="O16" t="n">
-        <v>14.46990436621835</v>
+        <v>14.47651615524844</v>
       </c>
       <c r="P16" t="n">
-        <v>281.5345612671321</v>
+        <v>281.4655343879937</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35293,28 +35379,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7705338933853405</v>
+        <v>-0.7659707453726891</v>
       </c>
       <c r="J17" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K17" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1712641380165344</v>
+        <v>0.1700157487747233</v>
       </c>
       <c r="M17" t="n">
-        <v>9.420106199727824</v>
+        <v>9.42745537719841</v>
       </c>
       <c r="N17" t="n">
-        <v>174.7408003666646</v>
+        <v>174.6062346640001</v>
       </c>
       <c r="O17" t="n">
-        <v>13.21895609973286</v>
+        <v>13.21386524314518</v>
       </c>
       <c r="P17" t="n">
-        <v>279.6183019666687</v>
+        <v>279.5737644126293</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35371,28 +35457,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9049086467562687</v>
+        <v>-0.9009462068487384</v>
       </c>
       <c r="J18" t="n">
+        <v>432</v>
+      </c>
+      <c r="K18" t="n">
         <v>431</v>
       </c>
-      <c r="K18" t="n">
-        <v>430</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3700842155575129</v>
+        <v>0.3685469224729556</v>
       </c>
       <c r="M18" t="n">
-        <v>6.66313058601274</v>
+        <v>6.667562593654627</v>
       </c>
       <c r="N18" t="n">
-        <v>85.40956945038059</v>
+        <v>85.41972133435281</v>
       </c>
       <c r="O18" t="n">
-        <v>9.241729786700139</v>
+        <v>9.242279011929515</v>
       </c>
       <c r="P18" t="n">
-        <v>285.3078284344188</v>
+        <v>285.2694560012372</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35449,28 +35535,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.178605996626982</v>
+        <v>-1.177072266319329</v>
       </c>
       <c r="J19" t="n">
+        <v>432</v>
+      </c>
+      <c r="K19" t="n">
         <v>431</v>
       </c>
-      <c r="K19" t="n">
-        <v>430</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.4472491461687398</v>
+        <v>0.4476736434971672</v>
       </c>
       <c r="M19" t="n">
-        <v>8.313876765700783</v>
+        <v>8.300956989452001</v>
       </c>
       <c r="N19" t="n">
-        <v>105.204016951025</v>
+        <v>104.9911345010749</v>
       </c>
       <c r="O19" t="n">
-        <v>10.2569009428299</v>
+        <v>10.24651816477553</v>
       </c>
       <c r="P19" t="n">
-        <v>294.5973297388037</v>
+        <v>294.5824770305929</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35508,7 +35594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T432"/>
+  <dimension ref="A1:T433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79359,6 +79445,108 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-35.39697815527582,173.23955058956454</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-35.3964063188378,173.23898734571995</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-35.395865877662246,173.23838113133513</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-35.395308682791054,173.23779783990906</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-35.394748242391465,173.2372189850629</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-35.394225440409045,173.23658861552548</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-35.39363071276931,173.23605667402884</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-35.39312453285781,173.23540354633033</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-35.39254192518354,173.23485500814263</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-35.39196099504682,173.23430416914002</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-35.39136007018962,173.2337806887034</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-35.390771869191006,173.23323979009422</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>-35.39014254187395,173.2327551693744</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-35.38965513009005,173.23207632669042</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>-35.38912166879499,173.2314604993959</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>-35.38856383041308,173.23087802813123</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>-35.388021836976954,173.2302738672799</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>-35.38745264522231,173.22970692353613</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T433"/>
+  <dimension ref="A1:T436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28932,6 +28932,204 @@
         <v>267.3</v>
       </c>
       <c r="T433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="C434" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="D434" t="n">
+        <v>302.55</v>
+      </c>
+      <c r="E434" t="n">
+        <v>300.81</v>
+      </c>
+      <c r="F434" t="n">
+        <v>298.53</v>
+      </c>
+      <c r="G434" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="H434" t="n">
+        <v>294.53</v>
+      </c>
+      <c r="I434" t="n">
+        <v>301.29</v>
+      </c>
+      <c r="J434" t="n">
+        <v>295.32</v>
+      </c>
+      <c r="K434" t="n">
+        <v>289.63</v>
+      </c>
+      <c r="L434" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="M434" t="n">
+        <v>273.71</v>
+      </c>
+      <c r="N434" t="n">
+        <v>259.96</v>
+      </c>
+      <c r="O434" t="n">
+        <v>269.85</v>
+      </c>
+      <c r="P434" t="n">
+        <v>272.07</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="R434" t="n">
+        <v>271.03</v>
+      </c>
+      <c r="S434" t="n">
+        <v>267.3</v>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>315.57</v>
+      </c>
+      <c r="C435" t="n">
+        <v>306.29</v>
+      </c>
+      <c r="D435" t="n">
+        <v>304.12</v>
+      </c>
+      <c r="E435" t="n">
+        <v>301.31</v>
+      </c>
+      <c r="F435" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="G435" t="n">
+        <v>304.58</v>
+      </c>
+      <c r="H435" t="n">
+        <v>296.59</v>
+      </c>
+      <c r="I435" t="n">
+        <v>303.5</v>
+      </c>
+      <c r="J435" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="K435" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="L435" t="n">
+        <v>290.37</v>
+      </c>
+      <c r="M435" t="n">
+        <v>274.06</v>
+      </c>
+      <c r="N435" t="n">
+        <v>258.78</v>
+      </c>
+      <c r="O435" t="n">
+        <v>270.84</v>
+      </c>
+      <c r="P435" t="n">
+        <v>273.24</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>270.46</v>
+      </c>
+      <c r="R435" t="n">
+        <v>271.21</v>
+      </c>
+      <c r="S435" t="n">
+        <v>266.77</v>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>319.12</v>
+      </c>
+      <c r="C436" t="n">
+        <v>306.53</v>
+      </c>
+      <c r="D436" t="n">
+        <v>303.54</v>
+      </c>
+      <c r="E436" t="n">
+        <v>327.51</v>
+      </c>
+      <c r="F436" t="n">
+        <v>326.07</v>
+      </c>
+      <c r="G436" t="n">
+        <v>330.57</v>
+      </c>
+      <c r="H436" t="n">
+        <v>315.3</v>
+      </c>
+      <c r="I436" t="n">
+        <v>315.13</v>
+      </c>
+      <c r="J436" t="n">
+        <v>300.66</v>
+      </c>
+      <c r="K436" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="L436" t="n">
+        <v>291.88</v>
+      </c>
+      <c r="M436" t="n">
+        <v>272.34</v>
+      </c>
+      <c r="N436" t="n">
+        <v>259.21</v>
+      </c>
+      <c r="O436" t="n">
+        <v>270.26</v>
+      </c>
+      <c r="P436" t="n">
+        <v>272.46</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>268.97</v>
+      </c>
+      <c r="R436" t="n">
+        <v>269.02</v>
+      </c>
+      <c r="S436" t="n">
+        <v>264.65</v>
+      </c>
+      <c r="T436" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28948,7 +29146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34041,6 +34239,26 @@
       </c>
       <c r="B509" t="n">
         <v>-0.16</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.22</v>
       </c>
     </row>
   </sheetData>
@@ -34209,28 +34427,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6689866442843282</v>
+        <v>-0.643360592309748</v>
       </c>
       <c r="J2" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K2" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08059702486316989</v>
+        <v>0.07526072146818052</v>
       </c>
       <c r="M2" t="n">
-        <v>14.58265634452935</v>
+        <v>14.61908414239435</v>
       </c>
       <c r="N2" t="n">
-        <v>307.8778960091722</v>
+        <v>308.8104813504067</v>
       </c>
       <c r="O2" t="n">
-        <v>17.54644966963893</v>
+        <v>17.57300433478597</v>
       </c>
       <c r="P2" t="n">
-        <v>310.6562218940967</v>
+        <v>310.4027841065729</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34287,28 +34505,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6699049983197874</v>
+        <v>-0.6472600034726343</v>
       </c>
       <c r="J3" t="n">
+        <v>435</v>
+      </c>
+      <c r="K3" t="n">
         <v>432</v>
       </c>
-      <c r="K3" t="n">
-        <v>429</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1015281675306614</v>
+        <v>0.09579065029042266</v>
       </c>
       <c r="M3" t="n">
-        <v>12.92854573849527</v>
+        <v>12.95953166189866</v>
       </c>
       <c r="N3" t="n">
-        <v>246.0202197996028</v>
+        <v>246.6533806410859</v>
       </c>
       <c r="O3" t="n">
-        <v>15.68503171178187</v>
+        <v>15.70520234320736</v>
       </c>
       <c r="P3" t="n">
-        <v>304.0278576079164</v>
+        <v>303.8089774441512</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34365,28 +34583,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9503813048408076</v>
+        <v>-0.9196780411206902</v>
       </c>
       <c r="J4" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K4" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1401229569261588</v>
+        <v>0.1325518160648538</v>
       </c>
       <c r="M4" t="n">
-        <v>11.1232206736616</v>
+        <v>11.18996391133368</v>
       </c>
       <c r="N4" t="n">
-        <v>342.6251527184708</v>
+        <v>344.502406058173</v>
       </c>
       <c r="O4" t="n">
-        <v>18.51013648567916</v>
+        <v>18.56077600905126</v>
       </c>
       <c r="P4" t="n">
-        <v>303.4061580203916</v>
+        <v>303.1093262520187</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34443,28 +34661,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.180777825843714</v>
+        <v>-1.134446171982328</v>
       </c>
       <c r="J5" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K5" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2954630388295173</v>
+        <v>0.2716723145170566</v>
       </c>
       <c r="M5" t="n">
-        <v>11.22348585970524</v>
+        <v>11.36626609975193</v>
       </c>
       <c r="N5" t="n">
-        <v>202.0740314092019</v>
+        <v>211.1557497771484</v>
       </c>
       <c r="O5" t="n">
-        <v>14.2152745808585</v>
+        <v>14.53119918579153</v>
       </c>
       <c r="P5" t="n">
-        <v>303.8679346079061</v>
+        <v>303.4129215306645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34521,28 +34739,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.215895482482945</v>
+        <v>-1.170653266217054</v>
       </c>
       <c r="J6" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K6" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2801330022700623</v>
+        <v>0.259419883763761</v>
       </c>
       <c r="M6" t="n">
-        <v>12.30298385107953</v>
+        <v>12.48343130009329</v>
       </c>
       <c r="N6" t="n">
-        <v>234.8426053258161</v>
+        <v>243.4939163427292</v>
       </c>
       <c r="O6" t="n">
-        <v>15.32457520865802</v>
+        <v>15.60429160015697</v>
       </c>
       <c r="P6" t="n">
-        <v>303.5558749972881</v>
+        <v>303.1181671819866</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34599,28 +34817,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.299221341866313</v>
+        <v>-1.243055143012768</v>
       </c>
       <c r="J7" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K7" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2685917733068616</v>
+        <v>0.2443160404864722</v>
       </c>
       <c r="M7" t="n">
-        <v>13.4414380899805</v>
+        <v>13.69009354570982</v>
       </c>
       <c r="N7" t="n">
-        <v>284.7975381088353</v>
+        <v>298.147590813787</v>
       </c>
       <c r="O7" t="n">
-        <v>16.87594554710448</v>
+        <v>17.26695082560285</v>
       </c>
       <c r="P7" t="n">
-        <v>301.0334294130026</v>
+        <v>300.490835802509</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34677,28 +34895,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.426053506666061</v>
+        <v>-1.379003768677853</v>
       </c>
       <c r="J8" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K8" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2444425848506215</v>
+        <v>0.2299177381128009</v>
       </c>
       <c r="M8" t="n">
-        <v>15.10052739672341</v>
+        <v>15.25583722571637</v>
       </c>
       <c r="N8" t="n">
-        <v>389.4619652383766</v>
+        <v>397.3359312069178</v>
       </c>
       <c r="O8" t="n">
-        <v>19.73479073206444</v>
+        <v>19.93328701461246</v>
       </c>
       <c r="P8" t="n">
-        <v>301.3809801567706</v>
+        <v>300.9264894117773</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34755,28 +34973,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.025633704312289</v>
+        <v>-0.974705991847276</v>
       </c>
       <c r="J9" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K9" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1462105323562185</v>
+        <v>0.1319502337932802</v>
       </c>
       <c r="M9" t="n">
-        <v>15.56330104780229</v>
+        <v>15.74967754808549</v>
       </c>
       <c r="N9" t="n">
-        <v>380.5918705560495</v>
+        <v>389.8917309370401</v>
       </c>
       <c r="O9" t="n">
-        <v>19.50876394229141</v>
+        <v>19.7456762592989</v>
       </c>
       <c r="P9" t="n">
-        <v>292.150175733919</v>
+        <v>291.6583302504841</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34833,28 +35051,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.034458221874244</v>
+        <v>-0.9948177325668285</v>
       </c>
       <c r="J10" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K10" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1905457557842207</v>
+        <v>0.1771212403405439</v>
       </c>
       <c r="M10" t="n">
-        <v>13.34678093812722</v>
+        <v>13.46717955669935</v>
       </c>
       <c r="N10" t="n">
-        <v>283.9892642515168</v>
+        <v>289.1787978307767</v>
       </c>
       <c r="O10" t="n">
-        <v>16.85198101860778</v>
+        <v>17.005257946611</v>
       </c>
       <c r="P10" t="n">
-        <v>292.5468280497141</v>
+        <v>292.1657671942341</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34911,28 +35129,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.098138711786983</v>
+        <v>-1.051661103612456</v>
       </c>
       <c r="J11" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K11" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L11" t="n">
-        <v>0.191331540754785</v>
+        <v>0.1756866012430748</v>
       </c>
       <c r="M11" t="n">
-        <v>14.03306837641515</v>
+        <v>14.16800538239422</v>
       </c>
       <c r="N11" t="n">
-        <v>315.6113479470293</v>
+        <v>323.5429742594376</v>
       </c>
       <c r="O11" t="n">
-        <v>17.76545377824696</v>
+        <v>17.98730036051652</v>
       </c>
       <c r="P11" t="n">
-        <v>286.6862723143705</v>
+        <v>286.2374101524507</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34989,28 +35207,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.802416848935173</v>
+        <v>-0.7593913675603717</v>
       </c>
       <c r="J12" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K12" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08118930830690385</v>
+        <v>0.07302580877912068</v>
       </c>
       <c r="M12" t="n">
-        <v>16.93020478955631</v>
+        <v>17.03495208588268</v>
       </c>
       <c r="N12" t="n">
-        <v>442.7979704773992</v>
+        <v>447.8687528851381</v>
       </c>
       <c r="O12" t="n">
-        <v>21.04276527639367</v>
+        <v>21.16290983974411</v>
       </c>
       <c r="P12" t="n">
-        <v>277.1863274841362</v>
+        <v>276.7632471409258</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35067,28 +35285,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6202017414845357</v>
+        <v>-0.6021956918662129</v>
       </c>
       <c r="J13" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K13" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04770154810276805</v>
+        <v>0.04556111297492138</v>
       </c>
       <c r="M13" t="n">
-        <v>17.75783462259304</v>
+        <v>17.72791137573901</v>
       </c>
       <c r="N13" t="n">
-        <v>480.0668224922285</v>
+        <v>478.1776600209581</v>
       </c>
       <c r="O13" t="n">
-        <v>21.91042725489917</v>
+        <v>21.86727372172759</v>
       </c>
       <c r="P13" t="n">
-        <v>275.0931709526754</v>
+        <v>274.9204618396014</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35145,28 +35363,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.434850069312458</v>
+        <v>-1.419844045129461</v>
       </c>
       <c r="J14" t="n">
+        <v>435</v>
+      </c>
+      <c r="K14" t="n">
         <v>432</v>
       </c>
-      <c r="K14" t="n">
-        <v>429</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.2285801034287744</v>
+        <v>0.2268759070523191</v>
       </c>
       <c r="M14" t="n">
-        <v>16.34431352744853</v>
+        <v>16.31263516363185</v>
       </c>
       <c r="N14" t="n">
-        <v>432.1819453945802</v>
+        <v>430.2033125659586</v>
       </c>
       <c r="O14" t="n">
-        <v>20.7889861560053</v>
+        <v>20.74134307526778</v>
       </c>
       <c r="P14" t="n">
-        <v>284.8815517932435</v>
+        <v>284.73687449457</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35223,28 +35441,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.424063698978707</v>
+        <v>-0.4066315925197898</v>
       </c>
       <c r="J15" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K15" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03917126700422491</v>
+        <v>0.03644059958654999</v>
       </c>
       <c r="M15" t="n">
-        <v>12.95869419119415</v>
+        <v>12.98042404760485</v>
       </c>
       <c r="N15" t="n">
-        <v>269.9795054216642</v>
+        <v>269.4217344793872</v>
       </c>
       <c r="O15" t="n">
-        <v>16.43105308316129</v>
+        <v>16.41407123413893</v>
       </c>
       <c r="P15" t="n">
-        <v>267.5442204956163</v>
+        <v>267.3736097985206</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35301,28 +35519,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.004670573469824</v>
+        <v>-0.982920180795296</v>
       </c>
       <c r="J16" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K16" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2292714600951018</v>
+        <v>0.2222714815798302</v>
       </c>
       <c r="M16" t="n">
-        <v>10.9648518223272</v>
+        <v>11.04040771603758</v>
       </c>
       <c r="N16" t="n">
-        <v>209.5695199931692</v>
+        <v>210.2246832908358</v>
       </c>
       <c r="O16" t="n">
-        <v>14.47651615524844</v>
+        <v>14.49912698374753</v>
       </c>
       <c r="P16" t="n">
-        <v>281.4655343879937</v>
+        <v>281.2549059955109</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35379,28 +35597,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7659707453726891</v>
+        <v>-0.752925648203813</v>
       </c>
       <c r="J17" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K17" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1700157487747233</v>
+        <v>0.1665326351209659</v>
       </c>
       <c r="M17" t="n">
-        <v>9.42745537719841</v>
+        <v>9.447750727560104</v>
       </c>
       <c r="N17" t="n">
-        <v>174.6062346640001</v>
+        <v>174.145138246384</v>
       </c>
       <c r="O17" t="n">
-        <v>13.21386524314518</v>
+        <v>13.19640626255436</v>
       </c>
       <c r="P17" t="n">
-        <v>279.5737644126293</v>
+        <v>279.4459756559123</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35457,28 +35675,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9009462068487384</v>
+        <v>-0.8899824539596016</v>
       </c>
       <c r="J18" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K18" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3685469224729556</v>
+        <v>0.3645815147533669</v>
       </c>
       <c r="M18" t="n">
-        <v>6.667562593654627</v>
+        <v>6.677565027232638</v>
       </c>
       <c r="N18" t="n">
-        <v>85.41972133435281</v>
+        <v>85.37164791820319</v>
       </c>
       <c r="O18" t="n">
-        <v>9.242279011929515</v>
+        <v>9.239677912038017</v>
       </c>
       <c r="P18" t="n">
-        <v>285.2694560012372</v>
+        <v>285.1629049151663</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35535,28 +35753,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.177072266319329</v>
+        <v>-1.173771137072641</v>
       </c>
       <c r="J19" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K19" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4476736434971672</v>
+        <v>0.4495584645993471</v>
       </c>
       <c r="M19" t="n">
-        <v>8.300956989452001</v>
+        <v>8.257154249812883</v>
       </c>
       <c r="N19" t="n">
-        <v>104.9911345010749</v>
+        <v>104.3223702658086</v>
       </c>
       <c r="O19" t="n">
-        <v>10.24651816477553</v>
+        <v>10.21383230065036</v>
       </c>
       <c r="P19" t="n">
-        <v>294.5824770305929</v>
+        <v>294.5504179499242</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35594,7 +35812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T433"/>
+  <dimension ref="A1:T436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79547,6 +79765,312 @@
         </is>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:04+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-35.39697815527582,173.23955058956454</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-35.3964063188378,173.23898734571995</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-35.395865877662246,173.23838113133513</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-35.395308682791054,173.23779783990906</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-35.394748242391465,173.2372189850629</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-35.394225440409045,173.23658861552548</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-35.39363071276931,173.23605667402884</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-35.39312453285781,173.23540354633033</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-35.39254192518354,173.23485500814263</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-35.39196099504682,173.23430416914002</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-35.39141344031632,173.23370764943698</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-35.390771869191006,173.23323979009422</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>-35.39014254187395,173.2327551693744</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-35.38965513009005,173.23207632669042</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>-35.38912166879499,173.2314604993959</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>-35.38856383041308,173.23087802813123</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>-35.388021836976954,173.2302738672799</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>-35.38745264522231,173.22970692353613</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-35.39703753120973,173.23946933150506</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-35.39643507613564,173.23894799036367</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-35.39587530329176,173.2383682320226</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-35.395311684571574,173.23779373186224</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-35.39476006935746,173.23720279941384</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-35.3942378076353,173.23657169047442</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-35.39364307995146,173.2360397490519</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-35.39313780049728,173.23538538899172</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-35.39255081026651,173.2348428485272</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-35.39196651818578,173.23429661049101</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-35.39141866326222,173.23370050160705</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-35.39077397037023,173.23323691454647</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>-35.39013545791924,173.23276486402634</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>-35.38966107337626,173.2320681930545</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>-35.38912869264691,173.2314508869445</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>-35.38856521116463,173.23087613851072</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>-35.3880229175604,173.230272388451</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>-35.387449463516894,173.2297112778491</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-35.39705884409481,173.2394401640229</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-35.39643651700199,173.23894601848704</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-35.39587182121222,173.23837299737409</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-35.39546897767541,173.23757846978296</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-35.394913579576745,173.23699271418963</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-35.394393838601296,173.23635815504153</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-35.39375540507472,173.23588602730115</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-35.393207620654444,173.23528983692617</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-35.39257398351765,173.23481113492306</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-35.39206257270026,173.23416515556028</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-35.39142772837422,173.23368809560125</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-35.390763644574534,173.23325104580815</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>-35.39013803936046,173.23276133122965</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>-35.389657591451076,173.2320729582151</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>-35.389124010079044,173.2314572952456</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>-35.3885562662953,173.23088837996423</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>-35.38800977046063,173.23029038086653</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>-35.38743673669371,173.22972869509758</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T436"/>
+  <dimension ref="A1:T437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29076,10 +29076,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>319.12</v>
+        <v>335.53</v>
       </c>
       <c r="C436" t="n">
-        <v>306.53</v>
+        <v>319.93</v>
       </c>
       <c r="D436" t="n">
         <v>303.54</v>
@@ -29130,6 +29130,72 @@
         <v>264.65</v>
       </c>
       <c r="T436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="C437" t="n">
+        <v>320.62</v>
+      </c>
+      <c r="D437" t="n">
+        <v>302.58</v>
+      </c>
+      <c r="E437" t="n">
+        <v>331.03</v>
+      </c>
+      <c r="F437" t="n">
+        <v>327.99</v>
+      </c>
+      <c r="G437" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="H437" t="n">
+        <v>316.38</v>
+      </c>
+      <c r="I437" t="n">
+        <v>317.39</v>
+      </c>
+      <c r="J437" t="n">
+        <v>297.77</v>
+      </c>
+      <c r="K437" t="n">
+        <v>306.09</v>
+      </c>
+      <c r="L437" t="n">
+        <v>299.56</v>
+      </c>
+      <c r="M437" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="N437" t="n">
+        <v>263.43</v>
+      </c>
+      <c r="O437" t="n">
+        <v>275.02</v>
+      </c>
+      <c r="P437" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>276.83</v>
+      </c>
+      <c r="R437" t="n">
+        <v>279.54</v>
+      </c>
+      <c r="S437" t="n">
+        <v>270.77</v>
+      </c>
+      <c r="T437" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29146,7 +29212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B511"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34259,6 +34325,16 @@
       </c>
       <c r="B511" t="n">
         <v>-0.22</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -34427,28 +34503,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.643360592309748</v>
+        <v>-0.6135131519459263</v>
       </c>
       <c r="J2" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K2" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07526072146818052</v>
+        <v>0.06728698016347223</v>
       </c>
       <c r="M2" t="n">
-        <v>14.61908414239435</v>
+        <v>14.74555367208877</v>
       </c>
       <c r="N2" t="n">
-        <v>308.8104813504067</v>
+        <v>317.5481810653066</v>
       </c>
       <c r="O2" t="n">
-        <v>17.57300433478597</v>
+        <v>17.8198816232125</v>
       </c>
       <c r="P2" t="n">
-        <v>310.4027841065729</v>
+        <v>310.1058816922545</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34505,28 +34581,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6472600034726343</v>
+        <v>-0.6277655880511864</v>
       </c>
       <c r="J3" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K3" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09579065029042266</v>
+        <v>0.08959179197334499</v>
       </c>
       <c r="M3" t="n">
-        <v>12.95953166189866</v>
+        <v>13.03486633186365</v>
       </c>
       <c r="N3" t="n">
-        <v>246.6533806410859</v>
+        <v>250.3528682137479</v>
       </c>
       <c r="O3" t="n">
-        <v>15.70520234320736</v>
+        <v>15.8225430387706</v>
       </c>
       <c r="P3" t="n">
-        <v>303.8089774441512</v>
+        <v>303.6194043470073</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34583,28 +34659,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9196780411206902</v>
+        <v>-0.909873544164027</v>
       </c>
       <c r="J4" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K4" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1325518160648538</v>
+        <v>0.1302036067646596</v>
       </c>
       <c r="M4" t="n">
-        <v>11.18996391133368</v>
+        <v>11.21061753886311</v>
       </c>
       <c r="N4" t="n">
-        <v>344.502406058173</v>
+        <v>345.007416629851</v>
       </c>
       <c r="O4" t="n">
-        <v>18.56077600905126</v>
+        <v>18.57437526889803</v>
       </c>
       <c r="P4" t="n">
-        <v>303.1093262520187</v>
+        <v>303.0138236494976</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34661,28 +34737,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.134446171982328</v>
+        <v>-1.110333403648392</v>
       </c>
       <c r="J5" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K5" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2716723145170566</v>
+        <v>0.2572839598472662</v>
       </c>
       <c r="M5" t="n">
-        <v>11.36626609975193</v>
+        <v>11.45502986399229</v>
       </c>
       <c r="N5" t="n">
-        <v>211.1557497771484</v>
+        <v>218.3155156225293</v>
       </c>
       <c r="O5" t="n">
-        <v>14.53119918579153</v>
+        <v>14.77550390418308</v>
       </c>
       <c r="P5" t="n">
-        <v>303.4129215306645</v>
+        <v>303.1745164268562</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34739,28 +34815,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.170653266217054</v>
+        <v>-1.147668382360221</v>
       </c>
       <c r="J6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L6" t="n">
-        <v>0.259419883763761</v>
+        <v>0.2473298488234723</v>
       </c>
       <c r="M6" t="n">
-        <v>12.48343130009329</v>
+        <v>12.58830001620633</v>
       </c>
       <c r="N6" t="n">
-        <v>243.4939163427292</v>
+        <v>250.0534001922814</v>
       </c>
       <c r="O6" t="n">
-        <v>15.60429160015697</v>
+        <v>15.81307687302763</v>
       </c>
       <c r="P6" t="n">
-        <v>303.1181671819866</v>
+        <v>302.8942784667697</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34817,28 +34893,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.243055143012768</v>
+        <v>-1.216135357941609</v>
       </c>
       <c r="J7" t="n">
+        <v>436</v>
+      </c>
+      <c r="K7" t="n">
         <v>435</v>
       </c>
-      <c r="K7" t="n">
-        <v>434</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.2443160404864722</v>
+        <v>0.2313509486710548</v>
       </c>
       <c r="M7" t="n">
-        <v>13.69009354570982</v>
+        <v>13.82103644459338</v>
       </c>
       <c r="N7" t="n">
-        <v>298.147590813787</v>
+        <v>307.2483980617239</v>
       </c>
       <c r="O7" t="n">
-        <v>17.26695082560285</v>
+        <v>17.52850244777699</v>
       </c>
       <c r="P7" t="n">
-        <v>300.490835802509</v>
+        <v>300.2289626675131</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34895,28 +34971,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.379003768677853</v>
+        <v>-1.35762349230983</v>
       </c>
       <c r="J8" t="n">
+        <v>436</v>
+      </c>
+      <c r="K8" t="n">
         <v>435</v>
       </c>
-      <c r="K8" t="n">
-        <v>434</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2299177381128009</v>
+        <v>0.2225514298382111</v>
       </c>
       <c r="M8" t="n">
-        <v>15.25583722571637</v>
+        <v>15.34107142830618</v>
       </c>
       <c r="N8" t="n">
-        <v>397.3359312069178</v>
+        <v>402.5955357592271</v>
       </c>
       <c r="O8" t="n">
-        <v>19.93328701461246</v>
+        <v>20.0647834715261</v>
       </c>
       <c r="P8" t="n">
-        <v>300.9264894117773</v>
+        <v>300.718504095967</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34973,28 +35049,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.974705991847276</v>
+        <v>-0.9535032159351536</v>
       </c>
       <c r="J9" t="n">
+        <v>436</v>
+      </c>
+      <c r="K9" t="n">
         <v>435</v>
       </c>
-      <c r="K9" t="n">
-        <v>434</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1319502337932802</v>
+        <v>0.1257932648814429</v>
       </c>
       <c r="M9" t="n">
-        <v>15.74967754808549</v>
+        <v>15.83968093227821</v>
       </c>
       <c r="N9" t="n">
-        <v>389.8917309370401</v>
+        <v>395.0663764230437</v>
       </c>
       <c r="O9" t="n">
-        <v>19.7456762592989</v>
+        <v>19.87627672435267</v>
       </c>
       <c r="P9" t="n">
-        <v>291.6583302504841</v>
+        <v>291.4520716423992</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35051,28 +35127,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9948177325668285</v>
+        <v>-0.9816667149862852</v>
       </c>
       <c r="J10" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K10" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1771212403405439</v>
+        <v>0.1727730862880994</v>
       </c>
       <c r="M10" t="n">
-        <v>13.46717955669935</v>
+        <v>13.50619162772804</v>
       </c>
       <c r="N10" t="n">
-        <v>289.1787978307767</v>
+        <v>290.8627563271573</v>
       </c>
       <c r="O10" t="n">
-        <v>17.005257946611</v>
+        <v>17.05469895152527</v>
       </c>
       <c r="P10" t="n">
-        <v>292.1657671942341</v>
+        <v>292.0383938927997</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35129,28 +35205,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.051661103612456</v>
+        <v>-1.032012059700707</v>
       </c>
       <c r="J11" t="n">
+        <v>436</v>
+      </c>
+      <c r="K11" t="n">
         <v>435</v>
       </c>
-      <c r="K11" t="n">
-        <v>434</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1756866012430748</v>
+        <v>0.1686925860612318</v>
       </c>
       <c r="M11" t="n">
-        <v>14.16800538239422</v>
+        <v>14.23322566034373</v>
       </c>
       <c r="N11" t="n">
-        <v>323.5429742594376</v>
+        <v>327.9991903623148</v>
       </c>
       <c r="O11" t="n">
-        <v>17.98730036051652</v>
+        <v>18.11074792387975</v>
       </c>
       <c r="P11" t="n">
-        <v>286.2374101524507</v>
+        <v>286.0462942726182</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35207,28 +35283,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7593913675603717</v>
+        <v>-0.7414595752278426</v>
       </c>
       <c r="J12" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K12" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07302580877912068</v>
+        <v>0.06954330431271138</v>
       </c>
       <c r="M12" t="n">
-        <v>17.03495208588268</v>
+        <v>17.08822274395245</v>
       </c>
       <c r="N12" t="n">
-        <v>447.8687528851381</v>
+        <v>451.0742556457683</v>
       </c>
       <c r="O12" t="n">
-        <v>21.16290983974411</v>
+        <v>21.2385087905382</v>
       </c>
       <c r="P12" t="n">
-        <v>276.7632471409258</v>
+        <v>276.5856063199772</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35285,28 +35361,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6021956918662129</v>
+        <v>-0.5942903249648216</v>
       </c>
       <c r="J13" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K13" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04556111297492138</v>
+        <v>0.04454789668628722</v>
       </c>
       <c r="M13" t="n">
-        <v>17.72791137573901</v>
+        <v>17.72865931245313</v>
       </c>
       <c r="N13" t="n">
-        <v>478.1776600209581</v>
+        <v>477.9115733377502</v>
       </c>
       <c r="O13" t="n">
-        <v>21.86727372172759</v>
+        <v>21.86118874484529</v>
       </c>
       <c r="P13" t="n">
-        <v>274.9204618396014</v>
+        <v>274.8440449227058</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35363,28 +35439,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.419844045129461</v>
+        <v>-1.413138583468645</v>
       </c>
       <c r="J14" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K14" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2268759070523191</v>
+        <v>0.2257758474078916</v>
       </c>
       <c r="M14" t="n">
-        <v>16.31263516363185</v>
+        <v>16.31116539517614</v>
       </c>
       <c r="N14" t="n">
-        <v>430.2033125659586</v>
+        <v>429.8208181990005</v>
       </c>
       <c r="O14" t="n">
-        <v>20.74134307526778</v>
+        <v>20.73212044627854</v>
       </c>
       <c r="P14" t="n">
-        <v>284.73687449457</v>
+        <v>284.6717267014079</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35441,28 +35517,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4066315925197898</v>
+        <v>-0.3989103597145504</v>
       </c>
       <c r="J15" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K15" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03644059958654999</v>
+        <v>0.03517638110798615</v>
       </c>
       <c r="M15" t="n">
-        <v>12.98042404760485</v>
+        <v>13.00016089347723</v>
       </c>
       <c r="N15" t="n">
-        <v>269.4217344793872</v>
+        <v>269.5800992115571</v>
       </c>
       <c r="O15" t="n">
-        <v>16.41407123413893</v>
+        <v>16.41889457946414</v>
       </c>
       <c r="P15" t="n">
-        <v>267.3736097985206</v>
+        <v>267.2974692204182</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35519,28 +35595,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.982920180795296</v>
+        <v>-0.9732957853940968</v>
       </c>
       <c r="J16" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K16" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2222714815798302</v>
+        <v>0.2186749444124542</v>
       </c>
       <c r="M16" t="n">
-        <v>11.04040771603758</v>
+        <v>11.08121606090584</v>
       </c>
       <c r="N16" t="n">
-        <v>210.2246832908358</v>
+        <v>210.977803892741</v>
       </c>
       <c r="O16" t="n">
-        <v>14.49912698374753</v>
+        <v>14.52507500471997</v>
       </c>
       <c r="P16" t="n">
-        <v>281.2549059955109</v>
+        <v>281.1609985626598</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35597,28 +35673,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.752925648203813</v>
+        <v>-0.7456969757139913</v>
       </c>
       <c r="J17" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K17" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1665326351209659</v>
+        <v>0.1639633786435108</v>
       </c>
       <c r="M17" t="n">
-        <v>9.447750727560104</v>
+        <v>9.473859542682884</v>
       </c>
       <c r="N17" t="n">
-        <v>174.145138246384</v>
+        <v>174.4333424299372</v>
       </c>
       <c r="O17" t="n">
-        <v>13.19640626255436</v>
+        <v>13.20732154639756</v>
       </c>
       <c r="P17" t="n">
-        <v>279.4459756559123</v>
+        <v>279.3746234657945</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35675,28 +35751,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8899824539596016</v>
+        <v>-0.8825545285057386</v>
       </c>
       <c r="J18" t="n">
+        <v>436</v>
+      </c>
+      <c r="K18" t="n">
         <v>435</v>
       </c>
-      <c r="K18" t="n">
-        <v>434</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3645815147533669</v>
+        <v>0.3597891438934636</v>
       </c>
       <c r="M18" t="n">
-        <v>6.677565027232638</v>
+        <v>6.700032113311324</v>
       </c>
       <c r="N18" t="n">
-        <v>85.37164791820319</v>
+        <v>85.91226227464787</v>
       </c>
       <c r="O18" t="n">
-        <v>9.239677912038017</v>
+        <v>9.268886787238685</v>
       </c>
       <c r="P18" t="n">
-        <v>285.1629049151663</v>
+        <v>285.090156360243</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35753,28 +35829,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.173771137072641</v>
+        <v>-1.17074028241191</v>
       </c>
       <c r="J19" t="n">
+        <v>436</v>
+      </c>
+      <c r="K19" t="n">
         <v>435</v>
       </c>
-      <c r="K19" t="n">
-        <v>434</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.4495584645993471</v>
+        <v>0.4491332666512824</v>
       </c>
       <c r="M19" t="n">
-        <v>8.257154249812883</v>
+        <v>8.25077501526251</v>
       </c>
       <c r="N19" t="n">
-        <v>104.3223702658086</v>
+        <v>104.2052323570046</v>
       </c>
       <c r="O19" t="n">
-        <v>10.21383230065036</v>
+        <v>10.20809641201554</v>
       </c>
       <c r="P19" t="n">
-        <v>294.5504179499242</v>
+        <v>294.5207339825608</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35812,7 +35888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T436"/>
+  <dimension ref="A1:T437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79977,12 +80053,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>-35.39705884409481,173.2394401640229</t>
+          <t>-35.397157363564766,173.23930533610994</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>-35.39643651700199,173.23894601848704</t>
+          <t>-35.396516965322576,173.23883592193076</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -80066,6 +80142,108 @@
         </is>
       </c>
       <c r="T436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-35.39723282901654,173.2392020581996</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-35.396521107808,173.2388302527738</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-35.39586605776984,173.23838088485147</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-35.39549011015471,173.2375495490124</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-35.39492510633635,173.23697693927946</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-35.39440854715688,173.23633802564893</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-35.39376188882785,173.23587715398557</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-35.39322118844918,173.23527126874987</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-35.39255663359724,173.23483487904807</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-35.39205981113496,173.23416893489392</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-35.39147383435454,173.23362499746247</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-35.39079822397684,173.23320372249907</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>-35.39016337349895,173.23272666051523</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>-35.38968616724539,173.232033851023</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>-35.3891598497244,173.23140824707582</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>-35.38860345196781,173.23082380421252</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>-35.38807292454089,173.23020395149283</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>-35.387473476384,173.22967841510118</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T437"/>
+  <dimension ref="A1:T438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28860,7 +28860,7 @@
         <v>270</v>
       </c>
       <c r="R432" t="n">
-        <v>271</v>
+        <v>269.32</v>
       </c>
       <c r="S432" t="n">
         <v>267.61</v>
@@ -28926,7 +28926,7 @@
         <v>270.23</v>
       </c>
       <c r="R433" t="n">
-        <v>271.03</v>
+        <v>269.18</v>
       </c>
       <c r="S433" t="n">
         <v>267.3</v>
@@ -28974,10 +28974,10 @@
         <v>289.63</v>
       </c>
       <c r="L434" t="n">
-        <v>289.5</v>
+        <v>280.61</v>
       </c>
       <c r="M434" t="n">
-        <v>273.71</v>
+        <v>277</v>
       </c>
       <c r="N434" t="n">
         <v>259.96</v>
@@ -28992,7 +28992,7 @@
         <v>270.23</v>
       </c>
       <c r="R434" t="n">
-        <v>271.03</v>
+        <v>269.18</v>
       </c>
       <c r="S434" t="n">
         <v>267.3</v>
@@ -29040,10 +29040,10 @@
         <v>290.55</v>
       </c>
       <c r="L435" t="n">
-        <v>290.37</v>
+        <v>280.75</v>
       </c>
       <c r="M435" t="n">
-        <v>274.06</v>
+        <v>277.6</v>
       </c>
       <c r="N435" t="n">
         <v>258.78</v>
@@ -29058,7 +29058,7 @@
         <v>270.46</v>
       </c>
       <c r="R435" t="n">
-        <v>271.21</v>
+        <v>269.13</v>
       </c>
       <c r="S435" t="n">
         <v>266.77</v>
@@ -29079,37 +29079,37 @@
         <v>335.53</v>
       </c>
       <c r="C436" t="n">
-        <v>319.93</v>
+        <v>306.53</v>
       </c>
       <c r="D436" t="n">
         <v>303.54</v>
       </c>
       <c r="E436" t="n">
-        <v>327.51</v>
+        <v>298.06</v>
       </c>
       <c r="F436" t="n">
-        <v>326.07</v>
+        <v>298.6</v>
       </c>
       <c r="G436" t="n">
-        <v>330.57</v>
+        <v>302.56</v>
       </c>
       <c r="H436" t="n">
-        <v>315.3</v>
+        <v>292.28</v>
       </c>
       <c r="I436" t="n">
-        <v>315.13</v>
+        <v>300.3</v>
       </c>
       <c r="J436" t="n">
         <v>300.66</v>
       </c>
       <c r="K436" t="n">
-        <v>306.55</v>
+        <v>294.41</v>
       </c>
       <c r="L436" t="n">
-        <v>291.88</v>
+        <v>280.29</v>
       </c>
       <c r="M436" t="n">
-        <v>272.34</v>
+        <v>276.76</v>
       </c>
       <c r="N436" t="n">
         <v>259.21</v>
@@ -29124,7 +29124,7 @@
         <v>268.97</v>
       </c>
       <c r="R436" t="n">
-        <v>269.02</v>
+        <v>266.96</v>
       </c>
       <c r="S436" t="n">
         <v>264.65</v>
@@ -29145,37 +29145,37 @@
         <v>348.1</v>
       </c>
       <c r="C437" t="n">
-        <v>320.62</v>
+        <v>305.81</v>
       </c>
       <c r="D437" t="n">
         <v>302.58</v>
       </c>
       <c r="E437" t="n">
-        <v>331.03</v>
+        <v>297.27</v>
       </c>
       <c r="F437" t="n">
-        <v>327.99</v>
+        <v>297.34</v>
       </c>
       <c r="G437" t="n">
-        <v>333.02</v>
+        <v>301.35</v>
       </c>
       <c r="H437" t="n">
-        <v>316.38</v>
+        <v>290.23</v>
       </c>
       <c r="I437" t="n">
-        <v>317.39</v>
+        <v>300.77</v>
       </c>
       <c r="J437" t="n">
         <v>297.77</v>
       </c>
       <c r="K437" t="n">
-        <v>306.09</v>
+        <v>287.8</v>
       </c>
       <c r="L437" t="n">
-        <v>299.56</v>
+        <v>283.46</v>
       </c>
       <c r="M437" t="n">
-        <v>278.1</v>
+        <v>283.59</v>
       </c>
       <c r="N437" t="n">
         <v>263.43</v>
@@ -29190,12 +29190,78 @@
         <v>276.83</v>
       </c>
       <c r="R437" t="n">
-        <v>279.54</v>
+        <v>275.04</v>
       </c>
       <c r="S437" t="n">
         <v>270.77</v>
       </c>
       <c r="T437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>357.87</v>
+      </c>
+      <c r="C438" t="n">
+        <v>310.36</v>
+      </c>
+      <c r="D438" t="n">
+        <v>306.03</v>
+      </c>
+      <c r="E438" t="n">
+        <v>301.57</v>
+      </c>
+      <c r="F438" t="n">
+        <v>301.44</v>
+      </c>
+      <c r="G438" t="n">
+        <v>305.12</v>
+      </c>
+      <c r="H438" t="n">
+        <v>298.57</v>
+      </c>
+      <c r="I438" t="n">
+        <v>309.01</v>
+      </c>
+      <c r="J438" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="K438" t="n">
+        <v>299.06</v>
+      </c>
+      <c r="L438" t="n">
+        <v>293.5</v>
+      </c>
+      <c r="M438" t="n">
+        <v>297.06</v>
+      </c>
+      <c r="N438" t="n">
+        <v>278.41</v>
+      </c>
+      <c r="O438" t="n">
+        <v>281.9</v>
+      </c>
+      <c r="P438" t="n">
+        <v>284.49</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>281.25</v>
+      </c>
+      <c r="R438" t="n">
+        <v>280.56</v>
+      </c>
+      <c r="S438" t="n">
+        <v>274.44</v>
+      </c>
+      <c r="T438" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29212,7 +29278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34335,6 +34401,26 @@
       </c>
       <c r="B512" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -34503,28 +34589,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6135131519459263</v>
+        <v>-0.5866256390872377</v>
       </c>
       <c r="J2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K2" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06728698016347223</v>
+        <v>0.06045840736844121</v>
       </c>
       <c r="M2" t="n">
-        <v>14.74555367208877</v>
+        <v>14.85961391823406</v>
       </c>
       <c r="N2" t="n">
-        <v>317.5481810653066</v>
+        <v>326.2462383534091</v>
       </c>
       <c r="O2" t="n">
-        <v>17.8198816232125</v>
+        <v>18.06228773863957</v>
       </c>
       <c r="P2" t="n">
-        <v>310.1058816922545</v>
+        <v>309.8373070652623</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34581,28 +34667,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6277655880511864</v>
+        <v>-0.62963146830303</v>
       </c>
       <c r="J3" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K3" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08959179197334499</v>
+        <v>0.09116988658485348</v>
       </c>
       <c r="M3" t="n">
-        <v>13.03486633186365</v>
+        <v>12.99393922957388</v>
       </c>
       <c r="N3" t="n">
-        <v>250.3528682137479</v>
+        <v>247.6315941015825</v>
       </c>
       <c r="O3" t="n">
-        <v>15.8225430387706</v>
+        <v>15.73631450186423</v>
       </c>
       <c r="P3" t="n">
-        <v>303.6194043470073</v>
+        <v>303.6370241983418</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34659,28 +34745,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.909873544164027</v>
+        <v>-0.8987111043898758</v>
       </c>
       <c r="J4" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K4" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1302036067646596</v>
+        <v>0.1274066656762355</v>
       </c>
       <c r="M4" t="n">
-        <v>11.21061753886311</v>
+        <v>11.23809663122022</v>
       </c>
       <c r="N4" t="n">
-        <v>345.007416629851</v>
+        <v>345.8972158835093</v>
       </c>
       <c r="O4" t="n">
-        <v>18.57437526889803</v>
+        <v>18.59831217835396</v>
       </c>
       <c r="P4" t="n">
-        <v>303.0138236494976</v>
+        <v>302.9047451043016</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34737,28 +34823,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.110333403648392</v>
+        <v>-1.124827283638609</v>
       </c>
       <c r="J5" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K5" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2572839598472662</v>
+        <v>0.2722158161368102</v>
       </c>
       <c r="M5" t="n">
-        <v>11.45502986399229</v>
+        <v>11.358407657117</v>
       </c>
       <c r="N5" t="n">
-        <v>218.3155156225293</v>
+        <v>207.9931949018913</v>
       </c>
       <c r="O5" t="n">
-        <v>14.77550390418308</v>
+        <v>14.42196917559774</v>
       </c>
       <c r="P5" t="n">
-        <v>303.1745164268562</v>
+        <v>303.3169094622515</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34815,28 +34901,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.147668382360221</v>
+        <v>-1.159392545142215</v>
       </c>
       <c r="J6" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K6" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2473298488234723</v>
+        <v>0.258770844655386</v>
       </c>
       <c r="M6" t="n">
-        <v>12.58830001620633</v>
+        <v>12.49067257103802</v>
       </c>
       <c r="N6" t="n">
-        <v>250.0534001922814</v>
+        <v>240.7605167556519</v>
       </c>
       <c r="O6" t="n">
-        <v>15.81307687302763</v>
+        <v>15.51645954319644</v>
       </c>
       <c r="P6" t="n">
-        <v>302.8942784667697</v>
+        <v>303.0076089163617</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34893,28 +34979,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.216135357941609</v>
+        <v>-1.22513970861061</v>
       </c>
       <c r="J7" t="n">
+        <v>437</v>
+      </c>
+      <c r="K7" t="n">
         <v>436</v>
       </c>
-      <c r="K7" t="n">
-        <v>435</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.2313509486710548</v>
+        <v>0.2409543197539138</v>
       </c>
       <c r="M7" t="n">
-        <v>13.82103644459338</v>
+        <v>13.73411156361382</v>
       </c>
       <c r="N7" t="n">
-        <v>307.2483980617239</v>
+        <v>296.3373790674019</v>
       </c>
       <c r="O7" t="n">
-        <v>17.52850244777699</v>
+        <v>17.21445262177691</v>
       </c>
       <c r="P7" t="n">
-        <v>300.2289626675131</v>
+        <v>300.3155682347225</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34971,28 +35057,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.35762349230983</v>
+        <v>-1.36369880675207</v>
       </c>
       <c r="J8" t="n">
+        <v>437</v>
+      </c>
+      <c r="K8" t="n">
         <v>436</v>
       </c>
-      <c r="K8" t="n">
-        <v>435</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2225514298382111</v>
+        <v>0.2275860541760061</v>
       </c>
       <c r="M8" t="n">
-        <v>15.34107142830618</v>
+        <v>15.27068501075485</v>
       </c>
       <c r="N8" t="n">
-        <v>402.5955357592271</v>
+        <v>395.5700367626235</v>
       </c>
       <c r="O8" t="n">
-        <v>20.0647834715261</v>
+        <v>19.88894257527593</v>
       </c>
       <c r="P8" t="n">
-        <v>300.718504095967</v>
+        <v>300.7767493345356</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35049,28 +35135,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9535032159351536</v>
+        <v>-0.9486906925688876</v>
       </c>
       <c r="J9" t="n">
+        <v>437</v>
+      </c>
+      <c r="K9" t="n">
         <v>436</v>
       </c>
-      <c r="K9" t="n">
-        <v>435</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1257932648814429</v>
+        <v>0.1257139313449086</v>
       </c>
       <c r="M9" t="n">
-        <v>15.83968093227821</v>
+        <v>15.83178618070976</v>
       </c>
       <c r="N9" t="n">
-        <v>395.0663764230437</v>
+        <v>392.284760061894</v>
       </c>
       <c r="O9" t="n">
-        <v>19.87627672435267</v>
+        <v>19.80617984523754</v>
       </c>
       <c r="P9" t="n">
-        <v>291.4520716423992</v>
+        <v>291.4044346349833</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35127,28 +35213,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9816667149862852</v>
+        <v>-0.9647704608797426</v>
       </c>
       <c r="J10" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K10" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1727730862880994</v>
+        <v>0.1666572228062145</v>
       </c>
       <c r="M10" t="n">
-        <v>13.50619162772804</v>
+        <v>13.5663831532982</v>
       </c>
       <c r="N10" t="n">
-        <v>290.8627563271573</v>
+        <v>294.0779510611497</v>
       </c>
       <c r="O10" t="n">
-        <v>17.05469895152527</v>
+        <v>17.14870114793391</v>
       </c>
       <c r="P10" t="n">
-        <v>292.0383938927997</v>
+        <v>291.8742124419375</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35205,28 +35291,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.032012059700707</v>
+        <v>-1.027796767028248</v>
       </c>
       <c r="J11" t="n">
+        <v>437</v>
+      </c>
+      <c r="K11" t="n">
         <v>436</v>
       </c>
-      <c r="K11" t="n">
-        <v>435</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1686925860612318</v>
+        <v>0.1689626593803916</v>
       </c>
       <c r="M11" t="n">
-        <v>14.23322566034373</v>
+        <v>14.22075385695323</v>
       </c>
       <c r="N11" t="n">
-        <v>327.9991903623148</v>
+        <v>325.4611098466262</v>
       </c>
       <c r="O11" t="n">
-        <v>18.11074792387975</v>
+        <v>18.04054073043894</v>
       </c>
       <c r="P11" t="n">
-        <v>286.0462942726182</v>
+        <v>286.0045537651905</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35283,28 +35369,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7414595752278426</v>
+        <v>-0.7451793607083251</v>
       </c>
       <c r="J12" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K12" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06954330431271138</v>
+        <v>0.07100390236228926</v>
       </c>
       <c r="M12" t="n">
-        <v>17.08822274395245</v>
+        <v>17.02813012150428</v>
       </c>
       <c r="N12" t="n">
-        <v>451.0742556457683</v>
+        <v>446.5768034723479</v>
       </c>
       <c r="O12" t="n">
-        <v>21.2385087905382</v>
+        <v>21.13236388746768</v>
       </c>
       <c r="P12" t="n">
-        <v>276.5856063199772</v>
+        <v>276.6210800149024</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35361,28 +35447,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5942903249648216</v>
+        <v>-0.5718079272984706</v>
       </c>
       <c r="J13" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K13" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04454789668628722</v>
+        <v>0.0411747534977388</v>
       </c>
       <c r="M13" t="n">
-        <v>17.72865931245313</v>
+        <v>17.80700664706136</v>
       </c>
       <c r="N13" t="n">
-        <v>477.9115733377502</v>
+        <v>481.4950412130188</v>
       </c>
       <c r="O13" t="n">
-        <v>21.86118874484529</v>
+        <v>21.94299526530093</v>
       </c>
       <c r="P13" t="n">
-        <v>274.8440449227058</v>
+        <v>274.6265556913468</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35439,28 +35525,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.413138583468645</v>
+        <v>-1.400304487388542</v>
       </c>
       <c r="J14" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K14" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2257758474078916</v>
+        <v>0.2225000524841793</v>
       </c>
       <c r="M14" t="n">
-        <v>16.31116539517614</v>
+        <v>16.34233748894292</v>
       </c>
       <c r="N14" t="n">
-        <v>429.8208181990005</v>
+        <v>431.0695463741707</v>
       </c>
       <c r="O14" t="n">
-        <v>20.73212044627854</v>
+        <v>20.76221438994817</v>
       </c>
       <c r="P14" t="n">
-        <v>284.6717267014079</v>
+        <v>284.5466307182887</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35517,28 +35603,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3989103597145504</v>
+        <v>-0.3883629533542999</v>
       </c>
       <c r="J15" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K15" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03517638110798615</v>
+        <v>0.03337631293895338</v>
       </c>
       <c r="M15" t="n">
-        <v>13.00016089347723</v>
+        <v>13.03838405506009</v>
       </c>
       <c r="N15" t="n">
-        <v>269.5800992115571</v>
+        <v>270.4235919747391</v>
       </c>
       <c r="O15" t="n">
-        <v>16.41889457946414</v>
+        <v>16.44456116698585</v>
       </c>
       <c r="P15" t="n">
-        <v>267.2974692204182</v>
+        <v>267.193125329363</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35595,28 +35681,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9732957853940968</v>
+        <v>-0.9612151908966988</v>
       </c>
       <c r="J16" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K16" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2186749444124542</v>
+        <v>0.2136657632049419</v>
       </c>
       <c r="M16" t="n">
-        <v>11.08121606090584</v>
+        <v>11.1383032897619</v>
       </c>
       <c r="N16" t="n">
-        <v>210.977803892741</v>
+        <v>212.4445516310364</v>
       </c>
       <c r="O16" t="n">
-        <v>14.52507500471997</v>
+        <v>14.57547774966695</v>
       </c>
       <c r="P16" t="n">
-        <v>281.1609985626598</v>
+        <v>281.0427468183025</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35673,28 +35759,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7456969757139913</v>
+        <v>-0.7366703238782651</v>
       </c>
       <c r="J17" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K17" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1639633786435108</v>
+        <v>0.1604457947295503</v>
       </c>
       <c r="M17" t="n">
-        <v>9.473859542682884</v>
+        <v>9.511395301589189</v>
       </c>
       <c r="N17" t="n">
-        <v>174.4333424299372</v>
+        <v>175.1087734013341</v>
       </c>
       <c r="O17" t="n">
-        <v>13.20732154639756</v>
+        <v>13.23286716480348</v>
       </c>
       <c r="P17" t="n">
-        <v>279.3746234657945</v>
+        <v>279.2852406096054</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35751,28 +35837,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8825545285057386</v>
+        <v>-0.8804393785585304</v>
       </c>
       <c r="J18" t="n">
+        <v>437</v>
+      </c>
+      <c r="K18" t="n">
         <v>436</v>
       </c>
-      <c r="K18" t="n">
-        <v>435</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3597891438934636</v>
+        <v>0.3593307753686743</v>
       </c>
       <c r="M18" t="n">
-        <v>6.700032113311324</v>
+        <v>6.694806382376948</v>
       </c>
       <c r="N18" t="n">
-        <v>85.91226227464787</v>
+        <v>85.87234776816628</v>
       </c>
       <c r="O18" t="n">
-        <v>9.268886787238685</v>
+        <v>9.266733392526531</v>
       </c>
       <c r="P18" t="n">
-        <v>285.090156360243</v>
+        <v>285.0688339604993</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35829,28 +35915,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.17074028241191</v>
+        <v>-1.16619066722063</v>
       </c>
       <c r="J19" t="n">
+        <v>437</v>
+      </c>
+      <c r="K19" t="n">
         <v>436</v>
       </c>
-      <c r="K19" t="n">
-        <v>435</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.4491332666512824</v>
+        <v>0.447697809374403</v>
       </c>
       <c r="M19" t="n">
-        <v>8.25077501526251</v>
+        <v>8.250823278327722</v>
       </c>
       <c r="N19" t="n">
-        <v>104.2052323570046</v>
+        <v>104.2427574832605</v>
       </c>
       <c r="O19" t="n">
-        <v>10.20809641201554</v>
+        <v>10.2099342546003</v>
       </c>
       <c r="P19" t="n">
-        <v>294.5207339825608</v>
+        <v>294.4760333018953</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35888,7 +35974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T437"/>
+  <dimension ref="A1:T438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79725,7 +79811,7 @@
       </c>
       <c r="R432" t="inlineStr">
         <is>
-          <t>-35.388021656879715,173.23027411375134</t>
+          <t>-35.38801157143337,173.2302879161524</t>
         </is>
       </c>
       <c r="S432" t="inlineStr">
@@ -79827,7 +79913,7 @@
       </c>
       <c r="R433" t="inlineStr">
         <is>
-          <t>-35.388021836976954,173.2302738672799</t>
+          <t>-35.388010730979424,173.23028906635233</t>
         </is>
       </c>
       <c r="S433" t="inlineStr">
@@ -79899,12 +79985,12 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>-35.39141344031632,173.23370764943698</t>
+          <t>-35.39136007018962,173.2337806887034</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>-35.390771869191006,173.23323979009422</t>
+          <t>-35.390791620272964,173.2332127599397</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -79929,7 +80015,7 @@
       </c>
       <c r="R434" t="inlineStr">
         <is>
-          <t>-35.388021836976954,173.2302738672799</t>
+          <t>-35.388010730979424,173.23028906635233</t>
         </is>
       </c>
       <c r="S434" t="inlineStr">
@@ -80001,12 +80087,12 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>-35.39141866326222,173.23370050160705</t>
+          <t>-35.3913609106644,173.2337795384795</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>-35.39077397037023,173.23323691454647</t>
+          <t>-35.390795222293335,173.2332078304268</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -80031,7 +80117,7 @@
       </c>
       <c r="R435" t="inlineStr">
         <is>
-          <t>-35.3880229175604,173.230272388451</t>
+          <t>-35.38801043081731,173.23028947713803</t>
         </is>
       </c>
       <c r="S435" t="inlineStr">
@@ -80058,7 +80144,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>-35.396516965322576,173.23883592193076</t>
+          <t>-35.39643651700199,173.23894601848704</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -80068,27 +80154,27 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>-35.39546897767541,173.23757846978296</t>
+          <t>-35.39529217299564,173.23782043416108</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>-35.394913579576745,173.23699271418963</t>
+          <t>-35.39474866263903,173.2372184099384</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>-35.394393838601296,173.23635815504153</t>
+          <t>-35.39422568054939,173.23658828688374</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>-35.39375540507472,173.23588602730115</t>
+          <t>-35.393617204922016,173.23607516004145</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>-35.393207620654444,173.23528983692617</t>
+          <t>-35.39311858943473,173.23541168015882</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -80098,17 +80184,17 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>-35.39206257270026,173.23416515556028</t>
+          <t>-35.391989691350524,173.2342648970175</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>-35.39142772837422,173.23368809560125</t>
+          <t>-35.39135814910438,173.2337833177866</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>-35.390763644574534,173.23325104580815</t>
+          <t>-35.390790179464766,173.2332147317447</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -80133,7 +80219,7 @@
       </c>
       <c r="R436" t="inlineStr">
         <is>
-          <t>-35.38800977046063,173.23029038086653</t>
+          <t>-35.38799740377986,173.2303073052338</t>
         </is>
       </c>
       <c r="S436" t="inlineStr">
@@ -80160,7 +80246,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>-35.396521107808,173.2388302527738</t>
+          <t>-35.39643219440281,173.2389519341167</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -80170,27 +80256,27 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>-35.39549011015471,173.2375495490124</t>
+          <t>-35.3952874301809,173.23782692487177</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>-35.39492510633635,173.23697693927946</t>
+          <t>-35.394741098182536,173.23722876217857</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>-35.39440854715688,173.23633802564893</t>
+          <t>-35.39421841630376,173.2365982282949</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>-35.39376188882785,173.23587715398557</t>
+          <t>-35.39360489776977,173.23609200284756</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>-35.39322118844918,173.23527126874987</t>
+          <t>-35.39312141105991,173.23540781864443</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -80200,17 +80286,17 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>-35.39205981113496,173.23416893489392</t>
+          <t>-35.39195000880166,173.2343192042758</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>-35.39147383435454,173.23362499746247</t>
+          <t>-35.39137717985261,173.23375727342602</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>-35.39079822397684,173.23320372249907</t>
+          <t>-35.390831182452345,173.23315861743245</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -80235,7 +80321,7 @@
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>-35.38807292454089,173.23020395149283</t>
+          <t>-35.38804590997042,173.23024092224904</t>
         </is>
       </c>
       <c r="S437" t="inlineStr">
@@ -80244,6 +80330,108 @@
         </is>
       </c>
       <c r="T437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-35.39729148428269,173.23912178557785</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-35.39645951082329,173.23891455061306</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-35.395886770138524,173.23835253922434</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-35.39531324549739,173.23779159567778</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-35.39476571268057,173.2371950763106</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-35.39424104952918,173.2365672538097</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-35.39365496685245,173.23602348135074</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-35.39317087953217,173.2353401188591</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-35.39261258557292,173.23475830626236</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-35.39201760719852,173.23422669293853</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-35.39143745385719,173.23367478584356</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>-35.39091204771147,173.23304794965443</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>-35.390253303606734,173.2326035875197</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>-35.38972747005172,173.23197732629325</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>-35.38919622964553,173.231358459442</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>-35.38862998638932,173.2307874905888</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>-35.38807904784196,173.23019557145133</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>-35.38749550818168,173.22964826351281</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T438"/>
+  <dimension ref="A1:T439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29010,7 +29010,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>315.57</v>
+        <v>308.05</v>
       </c>
       <c r="C435" t="n">
         <v>306.29</v>
@@ -29072,62 +29072,62 @@
     <row r="436">
       <c r="A436" s="1" t="inlineStr">
         <is>
-          <t>2026-01-24 22:12:07+00:00</t>
+          <t>2026-03-20 22:17:55+00:00</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>335.53</v>
+        <v>312.82</v>
       </c>
       <c r="C436" t="n">
-        <v>306.53</v>
+        <v>310.36</v>
       </c>
       <c r="D436" t="n">
-        <v>303.54</v>
+        <v>306.03</v>
       </c>
       <c r="E436" t="n">
-        <v>298.06</v>
+        <v>301.57</v>
       </c>
       <c r="F436" t="n">
-        <v>298.6</v>
+        <v>301.44</v>
       </c>
       <c r="G436" t="n">
-        <v>302.56</v>
+        <v>305.12</v>
       </c>
       <c r="H436" t="n">
-        <v>292.28</v>
+        <v>298.57</v>
       </c>
       <c r="I436" t="n">
-        <v>300.3</v>
+        <v>309.01</v>
       </c>
       <c r="J436" t="n">
-        <v>300.66</v>
+        <v>307.09</v>
       </c>
       <c r="K436" t="n">
-        <v>294.41</v>
+        <v>299.06</v>
       </c>
       <c r="L436" t="n">
-        <v>280.29</v>
+        <v>293.5</v>
       </c>
       <c r="M436" t="n">
-        <v>276.76</v>
+        <v>297.06</v>
       </c>
       <c r="N436" t="n">
-        <v>259.21</v>
+        <v>278.41</v>
       </c>
       <c r="O436" t="n">
-        <v>270.26</v>
+        <v>281.9</v>
       </c>
       <c r="P436" t="n">
-        <v>272.46</v>
+        <v>284.49</v>
       </c>
       <c r="Q436" t="n">
-        <v>268.97</v>
+        <v>281.25</v>
       </c>
       <c r="R436" t="n">
-        <v>266.96</v>
+        <v>280.56</v>
       </c>
       <c r="S436" t="n">
-        <v>264.65</v>
+        <v>274.44</v>
       </c>
       <c r="T436" t="inlineStr">
         <is>
@@ -29138,62 +29138,62 @@
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
         <is>
-          <t>2026-02-25 22:11:57+00:00</t>
+          <t>2026-03-29 22:11:43+00:00</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>348.1</v>
+        <v>315.8</v>
       </c>
       <c r="C437" t="n">
-        <v>305.81</v>
+        <v>307.19</v>
       </c>
       <c r="D437" t="n">
-        <v>302.58</v>
+        <v>307.01</v>
       </c>
       <c r="E437" t="n">
-        <v>297.27</v>
+        <v>303.15</v>
       </c>
       <c r="F437" t="n">
-        <v>297.34</v>
+        <v>303.87</v>
       </c>
       <c r="G437" t="n">
-        <v>301.35</v>
+        <v>308.37</v>
       </c>
       <c r="H437" t="n">
-        <v>290.23</v>
+        <v>311.69</v>
       </c>
       <c r="I437" t="n">
-        <v>300.77</v>
+        <v>313.73</v>
       </c>
       <c r="J437" t="n">
-        <v>297.77</v>
+        <v>314.8</v>
       </c>
       <c r="K437" t="n">
-        <v>287.8</v>
+        <v>308.87</v>
       </c>
       <c r="L437" t="n">
-        <v>283.46</v>
+        <v>299.16</v>
       </c>
       <c r="M437" t="n">
-        <v>283.59</v>
+        <v>304.25</v>
       </c>
       <c r="N437" t="n">
-        <v>263.43</v>
+        <v>278.41</v>
       </c>
       <c r="O437" t="n">
-        <v>275.02</v>
+        <v>285.95</v>
       </c>
       <c r="P437" t="n">
-        <v>278.43</v>
+        <v>288.41</v>
       </c>
       <c r="Q437" t="n">
-        <v>276.83</v>
+        <v>283.31</v>
       </c>
       <c r="R437" t="n">
-        <v>275.04</v>
+        <v>281.95</v>
       </c>
       <c r="S437" t="n">
-        <v>270.77</v>
+        <v>276.3</v>
       </c>
       <c r="T437" t="inlineStr">
         <is>
@@ -29204,64 +29204,130 @@
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
         <is>
-          <t>2026-03-20 22:17:55+00:00</t>
+          <t>2026-04-14 22:11:35+00:00</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>357.87</v>
+        <v>315.8</v>
       </c>
       <c r="C438" t="n">
-        <v>310.36</v>
+        <v>304.25</v>
       </c>
       <c r="D438" t="n">
-        <v>306.03</v>
+        <v>299.69</v>
       </c>
       <c r="E438" t="n">
-        <v>301.57</v>
+        <v>301.06</v>
       </c>
       <c r="F438" t="n">
-        <v>301.44</v>
+        <v>301.94</v>
       </c>
       <c r="G438" t="n">
-        <v>305.12</v>
+        <v>305</v>
       </c>
       <c r="H438" t="n">
-        <v>298.57</v>
+        <v>311.69</v>
       </c>
       <c r="I438" t="n">
-        <v>309.01</v>
+        <v>314.66</v>
       </c>
       <c r="J438" t="n">
-        <v>307.09</v>
+        <v>319.11</v>
       </c>
       <c r="K438" t="n">
-        <v>299.06</v>
+        <v>308.87</v>
       </c>
       <c r="L438" t="n">
-        <v>293.5</v>
+        <v>299.16</v>
       </c>
       <c r="M438" t="n">
-        <v>297.06</v>
+        <v>304.25</v>
       </c>
       <c r="N438" t="n">
         <v>278.41</v>
       </c>
       <c r="O438" t="n">
-        <v>281.9</v>
+        <v>285.95</v>
       </c>
       <c r="P438" t="n">
-        <v>284.49</v>
+        <v>288.41</v>
       </c>
       <c r="Q438" t="n">
-        <v>281.25</v>
+        <v>283.31</v>
       </c>
       <c r="R438" t="n">
-        <v>280.56</v>
+        <v>281.95</v>
       </c>
       <c r="S438" t="n">
-        <v>274.44</v>
+        <v>276.3</v>
       </c>
       <c r="T438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>314.06</v>
+      </c>
+      <c r="C439" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="D439" t="n">
+        <v>299.69</v>
+      </c>
+      <c r="E439" t="n">
+        <v>301.06</v>
+      </c>
+      <c r="F439" t="n">
+        <v>301.94</v>
+      </c>
+      <c r="G439" t="n">
+        <v>305</v>
+      </c>
+      <c r="H439" t="n">
+        <v>311.69</v>
+      </c>
+      <c r="I439" t="n">
+        <v>314.66</v>
+      </c>
+      <c r="J439" t="n">
+        <v>319.11</v>
+      </c>
+      <c r="K439" t="n">
+        <v>308.87</v>
+      </c>
+      <c r="L439" t="n">
+        <v>299.16</v>
+      </c>
+      <c r="M439" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="N439" t="n">
+        <v>278.41</v>
+      </c>
+      <c r="O439" t="n">
+        <v>285.95</v>
+      </c>
+      <c r="P439" t="n">
+        <v>288.41</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>280.12</v>
+      </c>
+      <c r="R439" t="n">
+        <v>279.66</v>
+      </c>
+      <c r="S439" t="n">
+        <v>277.46</v>
+      </c>
+      <c r="T439" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29278,7 +29344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34421,6 +34487,36 @@
       </c>
       <c r="B514" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -34589,28 +34685,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5866256390872377</v>
+        <v>-0.6212947181686719</v>
       </c>
       <c r="J2" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K2" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06045840736844121</v>
+        <v>0.07105336159333064</v>
       </c>
       <c r="M2" t="n">
-        <v>14.85961391823406</v>
+        <v>14.63273700037647</v>
       </c>
       <c r="N2" t="n">
-        <v>326.2462383534091</v>
+        <v>308.6817478677704</v>
       </c>
       <c r="O2" t="n">
-        <v>18.06228773863957</v>
+        <v>17.56934113357045</v>
       </c>
       <c r="P2" t="n">
-        <v>309.8373070652623</v>
+        <v>310.1804308273059</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34667,28 +34763,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.62963146830303</v>
+        <v>-0.6225383337387537</v>
       </c>
       <c r="J3" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K3" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09116988658485348</v>
+        <v>0.08950001439075916</v>
       </c>
       <c r="M3" t="n">
-        <v>12.99393922957388</v>
+        <v>13.00149676867587</v>
       </c>
       <c r="N3" t="n">
-        <v>247.6315941015825</v>
+        <v>247.7005192909274</v>
       </c>
       <c r="O3" t="n">
-        <v>15.73631450186423</v>
+        <v>15.73850435368391</v>
       </c>
       <c r="P3" t="n">
-        <v>303.6370241983418</v>
+        <v>303.5662359245544</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34745,28 +34841,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8987111043898758</v>
+        <v>-0.8895751183034778</v>
       </c>
       <c r="J4" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K4" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1274066656762355</v>
+        <v>0.1253318874210326</v>
       </c>
       <c r="M4" t="n">
-        <v>11.23809663122022</v>
+        <v>11.25629681608271</v>
       </c>
       <c r="N4" t="n">
-        <v>345.8972158835093</v>
+        <v>346.2364009011295</v>
       </c>
       <c r="O4" t="n">
-        <v>18.59831217835396</v>
+        <v>18.60742864828801</v>
       </c>
       <c r="P4" t="n">
-        <v>302.9047451043016</v>
+        <v>302.8136303792018</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34823,28 +34919,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.124827283638609</v>
+        <v>-1.109131770945712</v>
       </c>
       <c r="J5" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2722158161368102</v>
+        <v>0.264962808274218</v>
       </c>
       <c r="M5" t="n">
-        <v>11.358407657117</v>
+        <v>11.40467564932599</v>
       </c>
       <c r="N5" t="n">
-        <v>207.9931949018913</v>
+        <v>210.3898269526464</v>
       </c>
       <c r="O5" t="n">
-        <v>14.42196917559774</v>
+        <v>14.5048208176677</v>
       </c>
       <c r="P5" t="n">
-        <v>303.3169094622515</v>
+        <v>303.1591292995604</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34901,28 +34997,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.159392545142215</v>
+        <v>-1.142659597858418</v>
       </c>
       <c r="J6" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K6" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.258770844655386</v>
+        <v>0.2515642733437593</v>
       </c>
       <c r="M6" t="n">
-        <v>12.49067257103802</v>
+        <v>12.55613861265202</v>
       </c>
       <c r="N6" t="n">
-        <v>240.7605167556519</v>
+        <v>243.5370534463835</v>
       </c>
       <c r="O6" t="n">
-        <v>15.51645954319644</v>
+        <v>15.60567375816833</v>
       </c>
       <c r="P6" t="n">
-        <v>303.0076089163617</v>
+        <v>302.8418826844011</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34979,28 +35075,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.22513970861061</v>
+        <v>-1.205393039329855</v>
       </c>
       <c r="J7" t="n">
+        <v>438</v>
+      </c>
+      <c r="K7" t="n">
         <v>437</v>
       </c>
-      <c r="K7" t="n">
-        <v>436</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.2409543197539138</v>
+        <v>0.2330476608705602</v>
       </c>
       <c r="M7" t="n">
-        <v>13.73411156361382</v>
+        <v>13.81818764184136</v>
       </c>
       <c r="N7" t="n">
-        <v>296.3373790674019</v>
+        <v>300.4687481404522</v>
       </c>
       <c r="O7" t="n">
-        <v>17.21445262177691</v>
+        <v>17.33403438731019</v>
       </c>
       <c r="P7" t="n">
-        <v>300.3155682347225</v>
+        <v>300.1199908265161</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35057,28 +35153,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.36369880675207</v>
+        <v>-1.327085773674596</v>
       </c>
       <c r="J8" t="n">
+        <v>438</v>
+      </c>
+      <c r="K8" t="n">
         <v>437</v>
       </c>
-      <c r="K8" t="n">
-        <v>436</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2275860541760061</v>
+        <v>0.2139392653616337</v>
       </c>
       <c r="M8" t="n">
-        <v>15.27068501075485</v>
+        <v>15.44395478779711</v>
       </c>
       <c r="N8" t="n">
-        <v>395.5700367626235</v>
+        <v>406.6136097680793</v>
       </c>
       <c r="O8" t="n">
-        <v>19.88894257527593</v>
+        <v>20.16466240153996</v>
       </c>
       <c r="P8" t="n">
-        <v>300.7767493345356</v>
+        <v>300.4165627993847</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35135,28 +35231,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9486906925688876</v>
+        <v>-0.9170629077532438</v>
       </c>
       <c r="J9" t="n">
+        <v>438</v>
+      </c>
+      <c r="K9" t="n">
         <v>437</v>
       </c>
-      <c r="K9" t="n">
-        <v>436</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1257139313449086</v>
+        <v>0.1162149853333287</v>
       </c>
       <c r="M9" t="n">
-        <v>15.83178618070976</v>
+        <v>15.98457917016552</v>
       </c>
       <c r="N9" t="n">
-        <v>392.284760061894</v>
+        <v>401.8843353738933</v>
       </c>
       <c r="O9" t="n">
-        <v>19.80617984523754</v>
+        <v>20.0470530346456</v>
       </c>
       <c r="P9" t="n">
-        <v>291.4044346349833</v>
+        <v>291.0925381140324</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35213,28 +35309,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9647704608797426</v>
+        <v>-0.9279826885683942</v>
       </c>
       <c r="J10" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K10" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1666572228062145</v>
+        <v>0.1510253538246586</v>
       </c>
       <c r="M10" t="n">
-        <v>13.5663831532982</v>
+        <v>13.73212927827176</v>
       </c>
       <c r="N10" t="n">
-        <v>294.0779510611497</v>
+        <v>306.6665245295922</v>
       </c>
       <c r="O10" t="n">
-        <v>17.14870114793391</v>
+        <v>17.51189665711833</v>
       </c>
       <c r="P10" t="n">
-        <v>291.8742124419375</v>
+        <v>291.5133678009057</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35291,28 +35387,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.027796767028248</v>
+        <v>-0.9920514341898783</v>
       </c>
       <c r="J11" t="n">
+        <v>438</v>
+      </c>
+      <c r="K11" t="n">
         <v>437</v>
       </c>
-      <c r="K11" t="n">
-        <v>436</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1689626593803916</v>
+        <v>0.1549487251467896</v>
       </c>
       <c r="M11" t="n">
-        <v>14.22075385695323</v>
+        <v>14.36141364300713</v>
       </c>
       <c r="N11" t="n">
-        <v>325.4611098466262</v>
+        <v>337.1001063204696</v>
       </c>
       <c r="O11" t="n">
-        <v>18.04054073043894</v>
+        <v>18.3602861176091</v>
       </c>
       <c r="P11" t="n">
-        <v>286.0045537651905</v>
+        <v>285.6524879673867</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35369,28 +35465,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7451793607083251</v>
+        <v>-0.7127212580115876</v>
       </c>
       <c r="J12" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K12" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07100390236228926</v>
+        <v>0.06437368340753802</v>
       </c>
       <c r="M12" t="n">
-        <v>17.02813012150428</v>
+        <v>17.15245917019459</v>
       </c>
       <c r="N12" t="n">
-        <v>446.5768034723479</v>
+        <v>455.001007574525</v>
       </c>
       <c r="O12" t="n">
-        <v>21.13236388746768</v>
+        <v>21.33075262559962</v>
       </c>
       <c r="P12" t="n">
-        <v>276.6210800149024</v>
+        <v>276.2958717599552</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35447,28 +35543,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5718079272984706</v>
+        <v>-0.53320169543315</v>
       </c>
       <c r="J13" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K13" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0411747534977388</v>
+        <v>0.03533160825308945</v>
       </c>
       <c r="M13" t="n">
-        <v>17.80700664706136</v>
+        <v>17.9676316955228</v>
       </c>
       <c r="N13" t="n">
-        <v>481.4950412130188</v>
+        <v>492.1742637208499</v>
       </c>
       <c r="O13" t="n">
-        <v>21.94299526530093</v>
+        <v>22.18500087268085</v>
       </c>
       <c r="P13" t="n">
-        <v>274.6265556913468</v>
+        <v>274.249686155694</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35525,28 +35621,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.400304487388542</v>
+        <v>-1.37319632624322</v>
       </c>
       <c r="J14" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K14" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2225000524841793</v>
+        <v>0.21440485812445</v>
       </c>
       <c r="M14" t="n">
-        <v>16.34233748894292</v>
+        <v>16.45263404564151</v>
       </c>
       <c r="N14" t="n">
-        <v>431.0695463741707</v>
+        <v>435.8009914101741</v>
       </c>
       <c r="O14" t="n">
-        <v>20.76221438994817</v>
+        <v>20.87584708245809</v>
       </c>
       <c r="P14" t="n">
-        <v>284.5466307182887</v>
+        <v>284.2807135219861</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35603,28 +35699,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3883629533542999</v>
+        <v>-0.3648452509875413</v>
       </c>
       <c r="J15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K15" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03337631293895338</v>
+        <v>0.02922178534266129</v>
       </c>
       <c r="M15" t="n">
-        <v>13.03838405506009</v>
+        <v>13.16024206158784</v>
       </c>
       <c r="N15" t="n">
-        <v>270.4235919747391</v>
+        <v>274.483183547675</v>
       </c>
       <c r="O15" t="n">
-        <v>16.44456116698585</v>
+        <v>16.56753402132239</v>
       </c>
       <c r="P15" t="n">
-        <v>267.193125329363</v>
+        <v>266.9587295447939</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35681,28 +35777,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9612151908966988</v>
+        <v>-0.936521176560532</v>
       </c>
       <c r="J16" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K16" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2136657632049419</v>
+        <v>0.2016275732509787</v>
       </c>
       <c r="M16" t="n">
-        <v>11.1383032897619</v>
+        <v>11.27876639206772</v>
       </c>
       <c r="N16" t="n">
-        <v>212.4445516310364</v>
+        <v>217.5528876655366</v>
       </c>
       <c r="O16" t="n">
-        <v>14.57547774966695</v>
+        <v>14.74967415455462</v>
       </c>
       <c r="P16" t="n">
-        <v>281.0427468183025</v>
+        <v>280.7990134165689</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35759,28 +35855,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7366703238782651</v>
+        <v>-0.7192741267415308</v>
       </c>
       <c r="J17" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K17" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1604457947295503</v>
+        <v>0.1527989218283309</v>
       </c>
       <c r="M17" t="n">
-        <v>9.511395301589189</v>
+        <v>9.604307520112028</v>
       </c>
       <c r="N17" t="n">
-        <v>175.1087734013341</v>
+        <v>177.3520270095143</v>
       </c>
       <c r="O17" t="n">
-        <v>13.23286716480348</v>
+        <v>13.31735810923151</v>
       </c>
       <c r="P17" t="n">
-        <v>279.2852406096054</v>
+        <v>279.1116659091807</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35837,28 +35933,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8804393785585304</v>
+        <v>-0.8637596789857414</v>
       </c>
       <c r="J18" t="n">
+        <v>438</v>
+      </c>
+      <c r="K18" t="n">
         <v>437</v>
       </c>
-      <c r="K18" t="n">
-        <v>436</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3593307753686743</v>
+        <v>0.3460812030159739</v>
       </c>
       <c r="M18" t="n">
-        <v>6.694806382376948</v>
+        <v>6.762993679734921</v>
       </c>
       <c r="N18" t="n">
-        <v>85.87234776816628</v>
+        <v>87.81900766477007</v>
       </c>
       <c r="O18" t="n">
-        <v>9.266733392526531</v>
+        <v>9.371179630375787</v>
       </c>
       <c r="P18" t="n">
-        <v>285.0688339604993</v>
+        <v>284.9039328355216</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35915,28 +36011,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.16619066722063</v>
+        <v>-1.153124311321079</v>
       </c>
       <c r="J19" t="n">
+        <v>438</v>
+      </c>
+      <c r="K19" t="n">
         <v>437</v>
       </c>
-      <c r="K19" t="n">
-        <v>436</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.447697809374403</v>
+        <v>0.4408149264945579</v>
       </c>
       <c r="M19" t="n">
-        <v>8.250823278327722</v>
+        <v>8.286440797518342</v>
       </c>
       <c r="N19" t="n">
-        <v>104.2427574832605</v>
+        <v>105.0771771323413</v>
       </c>
       <c r="O19" t="n">
-        <v>10.2099342546003</v>
+        <v>10.25071593267228</v>
       </c>
       <c r="P19" t="n">
-        <v>294.4760333018953</v>
+        <v>294.3470502246007</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35974,7 +36070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T438"/>
+  <dimension ref="A1:T439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80037,7 +80133,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>-35.39703753120973,173.23946933150506</t>
+          <t>-35.39699238389187,173.2395311172194</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -80134,97 +80230,97 @@
     <row r="436">
       <c r="A436" s="1" t="inlineStr">
         <is>
-          <t>2026-01-24 22:12:07+00:00</t>
+          <t>2026-03-20 22:17:55+00:00</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>-35.397157363564766,173.23930533610994</t>
+          <t>-35.3970210212235,173.23949192602296</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>-35.39643651700199,173.23894601848704</t>
+          <t>-35.39645951082329,173.23891455061306</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>-35.39587182121222,173.23837299737409</t>
+          <t>-35.395886770138524,173.23835253922434</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>-35.39529217299564,173.23782043416108</t>
+          <t>-35.39531324549739,173.23779159567778</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>-35.39474866263903,173.2372184099384</t>
+          <t>-35.39476571268057,173.2371950763106</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>-35.39422568054939,173.23658828688374</t>
+          <t>-35.39424104952918,173.2365672538097</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>-35.393617204922016,173.23607516004145</t>
+          <t>-35.39365496685245,173.23602348135074</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>-35.39311858943473,173.23541168015882</t>
+          <t>-35.39317087953217,173.2353401188591</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>-35.39257398351765,173.23481113492306</t>
+          <t>-35.39261258557292,173.23475830626236</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>-35.391989691350524,173.2342648970175</t>
+          <t>-35.39201760719852,173.23422669293853</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>-35.39135814910438,173.2337833177866</t>
+          <t>-35.39143745385719,173.23367478584356</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>-35.390790179464766,173.2332147317447</t>
+          <t>-35.39091204771147,173.23304794965443</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>-35.39013803936046,173.23276133122965</t>
+          <t>-35.390253303606734,173.2326035875197</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>-35.389657591451076,173.2320729582151</t>
+          <t>-35.38972747005172,173.23197732629325</t>
         </is>
       </c>
       <c r="P436" t="inlineStr">
         <is>
-          <t>-35.389124010079044,173.2314572952456</t>
+          <t>-35.38919622964553,173.231358459442</t>
         </is>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
-          <t>-35.3885562662953,173.23088837996423</t>
+          <t>-35.38862998638932,173.2307874905888</t>
         </is>
       </c>
       <c r="R436" t="inlineStr">
         <is>
-          <t>-35.38799740377986,173.2303073052338</t>
+          <t>-35.38807904784196,173.23019557145133</t>
         </is>
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>-35.38743673669371,173.22972869509758</t>
+          <t>-35.38749550818168,173.22964826351281</t>
         </is>
       </c>
       <c r="T436" t="inlineStr">
@@ -80236,97 +80332,97 @@
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
         <is>
-          <t>2026-02-25 22:11:57+00:00</t>
+          <t>2026-03-29 22:11:43+00:00</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>-35.39723282901654,173.2392020581996</t>
+          <t>-35.39703891204475,173.23946744178136</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>-35.39643219440281,173.2389519341167</t>
+          <t>-35.39644047938432,173.23894059582597</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>-35.39586605776984,173.23838088485147</t>
+          <t>-35.395892653650726,173.23834448742033</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>-35.3952874301809,173.23782692487177</t>
+          <t>-35.39532273112271,173.23777861424736</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>-35.394741098182536,173.23722876217857</t>
+          <t>-35.394780301268874,173.2371751112621</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>-35.39421841630376,173.2365982282949</t>
+          <t>-35.39426056092402,173.2365405516534</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>-35.39360489776977,173.23609200284756</t>
+          <t>-35.39373373252479,173.23591568716975</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>-35.39312141105991,173.23540781864443</t>
+          <t>-35.39319921582439,173.23530133933318</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>-35.39255663359724,173.23483487904807</t>
+          <t>-35.39265887198814,173.23469496109888</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>-35.39195000880166,173.2343192042758</t>
+          <t>-35.39207650059296,173.23414609456944</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>-35.39137717985261,173.23375727342602</t>
+          <t>-35.39147143300222,173.23362828382562</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>-35.390831182452345,173.23315861743245</t>
+          <t>-35.390955211828235,173.2329888774538</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>-35.39016337349895,173.23272666051523</t>
+          <t>-35.390253303606734,173.2326035875197</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>-35.38968616724539,173.232033851023</t>
+          <t>-35.38975178346456,173.2319440522611</t>
         </is>
       </c>
       <c r="P437" t="inlineStr">
         <is>
-          <t>-35.3891598497244,173.23140824707582</t>
+          <t>-35.38921976252081,173.23132625355603</t>
         </is>
       </c>
       <c r="Q437" t="inlineStr">
         <is>
-          <t>-35.38860345196781,173.23082380421252</t>
+          <t>-35.388642353106924,173.2307705661316</t>
         </is>
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>-35.38804590997042,173.23024092224904</t>
+          <t>-35.388087392339536,173.2301841515888</t>
         </is>
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>-35.387473476384,173.22967841510118</t>
+          <t>-35.387506674158004,173.22963298232008</t>
         </is>
       </c>
       <c r="T437" t="inlineStr">
@@ -80338,67 +80434,67 @@
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
         <is>
-          <t>2026-03-20 22:17:55+00:00</t>
+          <t>2026-04-14 22:11:35+00:00</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>-35.39729148428269,173.23912178557785</t>
+          <t>-35.39703891204475,173.23946744178136</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>-35.39645951082329,173.23891455061306</t>
+          <t>-35.39642282877026,173.23896475131215</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>-35.395886770138524,173.23835253922434</t>
+          <t>-35.3958487074037,173.23840462943812</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>-35.39531324549739,173.23779159567778</t>
+          <t>-35.39531018368132,173.23779578588568</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>-35.39476571268057,173.2371950763106</t>
+          <t>-35.394768714447984,173.2371909682765</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>-35.39424104952918,173.2365672538097</t>
+          <t>-35.39424032910833,173.23656823973522</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>-35.39365496685245,173.23602348135074</t>
+          <t>-35.39373373252479,173.23591568716975</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>-35.39317087953217,173.2353401188591</t>
+          <t>-35.39320479903304,173.2352936984488</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>-35.39261258557292,173.23475830626236</t>
+          <t>-35.39268474674011,173.23465955021723</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>-35.39201760719852,173.23422669293853</t>
+          <t>-35.39207650059296,173.23414609456944</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>-35.39143745385719,173.23367478584356</t>
+          <t>-35.39147143300222,173.23362828382562</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>-35.39091204771147,173.23304794965443</t>
+          <t>-35.390955211828235,173.2329888774538</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -80408,30 +80504,132 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>-35.38972747005172,173.23197732629325</t>
+          <t>-35.38975178346456,173.2319440522611</t>
         </is>
       </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>-35.38919622964553,173.231358459442</t>
+          <t>-35.38921976252081,173.23132625355603</t>
         </is>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
-          <t>-35.38862998638932,173.2307874905888</t>
+          <t>-35.388642353106924,173.2307705661316</t>
         </is>
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>-35.38807904784196,173.23019557145133</t>
+          <t>-35.388087392339536,173.2301841515888</t>
         </is>
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>-35.38749550818168,173.22964826351281</t>
+          <t>-35.387506674158004,173.22963298232008</t>
         </is>
       </c>
       <c r="T438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-35.397028465726905,173.2394817379506</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-35.39642282877026,173.23896475131215</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-35.3958487074037,173.23840462943812</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-35.39531018368132,173.23779578588568</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-35.394768714447984,173.2371909682765</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-35.39424032910833,173.23656823973522</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-35.39373373252479,173.23591568716975</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-35.39320479903304,173.2352936984488</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-35.39268474674011,173.23465955021723</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-35.39207650059296,173.23414609456944</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-35.39147143300222,173.23362828382562</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>-35.390955211828235,173.2329888774538</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>-35.390253303606734,173.2326035875197</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>-35.38975178346456,173.2319440522611</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>-35.38921976252081,173.23132625355603</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>-35.38862320270342,173.2307967743908</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>-35.388073644929285,173.23020296560566</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>-35.387513637884176,173.22962345211172</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T439"/>
+  <dimension ref="A1:T442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29138,35 +29138,35 @@
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
         <is>
-          <t>2026-03-29 22:11:43+00:00</t>
+          <t>2026-04-14 22:11:35+00:00</t>
         </is>
       </c>
       <c r="B437" t="n">
         <v>315.8</v>
       </c>
       <c r="C437" t="n">
-        <v>307.19</v>
+        <v>314.57</v>
       </c>
       <c r="D437" t="n">
-        <v>307.01</v>
+        <v>299.69</v>
       </c>
       <c r="E437" t="n">
-        <v>303.15</v>
+        <v>301.06</v>
       </c>
       <c r="F437" t="n">
-        <v>303.87</v>
+        <v>301.94</v>
       </c>
       <c r="G437" t="n">
-        <v>308.37</v>
+        <v>305</v>
       </c>
       <c r="H437" t="n">
         <v>311.69</v>
       </c>
       <c r="I437" t="n">
-        <v>313.73</v>
+        <v>314.66</v>
       </c>
       <c r="J437" t="n">
-        <v>314.8</v>
+        <v>319.11</v>
       </c>
       <c r="K437" t="n">
         <v>308.87</v>
@@ -29204,14 +29204,14 @@
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
         <is>
-          <t>2026-04-14 22:11:35+00:00</t>
+          <t>2026-04-21 22:17:21+00:00</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>315.8</v>
+        <v>314.06</v>
       </c>
       <c r="C438" t="n">
-        <v>304.25</v>
+        <v>314.57</v>
       </c>
       <c r="D438" t="n">
         <v>299.69</v>
@@ -29253,13 +29253,13 @@
         <v>288.41</v>
       </c>
       <c r="Q438" t="n">
-        <v>283.31</v>
+        <v>280.12</v>
       </c>
       <c r="R438" t="n">
-        <v>281.95</v>
+        <v>279.66</v>
       </c>
       <c r="S438" t="n">
-        <v>276.3</v>
+        <v>277.46</v>
       </c>
       <c r="T438" t="inlineStr">
         <is>
@@ -29270,66 +29270,264 @@
     <row r="439">
       <c r="A439" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21 22:17:21+00:00</t>
+          <t>2026-04-22 22:11:20+00:00</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>314.06</v>
+        <v>304.37</v>
       </c>
       <c r="C439" t="n">
-        <v>304.25</v>
+        <v>314.75</v>
       </c>
       <c r="D439" t="n">
-        <v>299.69</v>
+        <v>300.16</v>
       </c>
       <c r="E439" t="n">
-        <v>301.06</v>
+        <v>298.93</v>
       </c>
       <c r="F439" t="n">
-        <v>301.94</v>
+        <v>301.47</v>
       </c>
       <c r="G439" t="n">
-        <v>305</v>
+        <v>306.1</v>
       </c>
       <c r="H439" t="n">
-        <v>311.69</v>
+        <v>310.59</v>
       </c>
       <c r="I439" t="n">
-        <v>314.66</v>
+        <v>313.57</v>
       </c>
       <c r="J439" t="n">
-        <v>319.11</v>
+        <v>317.32</v>
       </c>
       <c r="K439" t="n">
-        <v>308.87</v>
+        <v>311.26</v>
       </c>
       <c r="L439" t="n">
-        <v>299.16</v>
+        <v>302.75</v>
       </c>
       <c r="M439" t="n">
-        <v>304.25</v>
+        <v>303.89</v>
       </c>
       <c r="N439" t="n">
-        <v>278.41</v>
+        <v>279.43</v>
       </c>
       <c r="O439" t="n">
-        <v>285.95</v>
+        <v>287.62</v>
       </c>
       <c r="P439" t="n">
-        <v>288.41</v>
+        <v>284.9</v>
       </c>
       <c r="Q439" t="n">
-        <v>280.12</v>
+        <v>277.61</v>
       </c>
       <c r="R439" t="n">
-        <v>279.66</v>
+        <v>277.68</v>
       </c>
       <c r="S439" t="n">
-        <v>277.46</v>
+        <v>278.16</v>
       </c>
       <c r="T439" t="inlineStr">
         <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>298.92</v>
+      </c>
+      <c r="C440" t="n">
+        <v>314.75</v>
+      </c>
+      <c r="D440" t="n">
+        <v>297.46</v>
+      </c>
+      <c r="E440" t="n">
+        <v>296.6</v>
+      </c>
+      <c r="F440" t="n">
+        <v>299.96</v>
+      </c>
+      <c r="G440" t="n">
+        <v>301.72</v>
+      </c>
+      <c r="H440" t="n">
+        <v>306.66</v>
+      </c>
+      <c r="I440" t="n">
+        <v>308.98</v>
+      </c>
+      <c r="J440" t="n">
+        <v>312.39</v>
+      </c>
+      <c r="K440" t="n">
+        <v>311.26</v>
+      </c>
+      <c r="L440" t="n">
+        <v>299.26</v>
+      </c>
+      <c r="M440" t="n">
+        <v>301.83</v>
+      </c>
+      <c r="N440" t="n">
+        <v>276.37</v>
+      </c>
+      <c r="O440" t="n">
+        <v>283.93</v>
+      </c>
+      <c r="P440" t="n">
+        <v>282.14</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>275.96</v>
+      </c>
+      <c r="R440" t="n">
+        <v>275.86</v>
+      </c>
+      <c r="S440" t="n">
+        <v>275.54</v>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>298.92</v>
+      </c>
+      <c r="C441" t="n">
+        <v>314.75</v>
+      </c>
+      <c r="D441" t="n">
+        <v>294.87</v>
+      </c>
+      <c r="E441" t="n">
+        <v>295.1</v>
+      </c>
+      <c r="F441" t="n">
+        <v>298.82</v>
+      </c>
+      <c r="G441" t="n">
+        <v>300.1</v>
+      </c>
+      <c r="H441" t="n">
+        <v>305.09</v>
+      </c>
+      <c r="I441" t="n">
+        <v>308.98</v>
+      </c>
+      <c r="J441" t="n">
+        <v>312.39</v>
+      </c>
+      <c r="K441" t="n">
+        <v>311.26</v>
+      </c>
+      <c r="L441" t="n">
+        <v>299.26</v>
+      </c>
+      <c r="M441" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="N441" t="n">
+        <v>276.37</v>
+      </c>
+      <c r="O441" t="n">
+        <v>282.58</v>
+      </c>
+      <c r="P441" t="n">
+        <v>279.43</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>274.95</v>
+      </c>
+      <c r="R441" t="n">
+        <v>275.1</v>
+      </c>
+      <c r="S441" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>293.3</v>
+      </c>
+      <c r="C442" t="n">
+        <v>322.44</v>
+      </c>
+      <c r="D442" t="n">
+        <v>292.65</v>
+      </c>
+      <c r="E442" t="n">
+        <v>293.99</v>
+      </c>
+      <c r="F442" t="n">
+        <v>301.43</v>
+      </c>
+      <c r="G442" t="n">
+        <v>300.92</v>
+      </c>
+      <c r="H442" t="n">
+        <v>304.67</v>
+      </c>
+      <c r="I442" t="n">
+        <v>305.06</v>
+      </c>
+      <c r="J442" t="n">
+        <v>304.88</v>
+      </c>
+      <c r="K442" t="n">
+        <v>303.74</v>
+      </c>
+      <c r="L442" t="n">
+        <v>299.57</v>
+      </c>
+      <c r="M442" t="n">
+        <v>311.58</v>
+      </c>
+      <c r="N442" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="O442" t="n">
+        <v>283.16</v>
+      </c>
+      <c r="P442" t="n">
+        <v>274.84</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="R442" t="n">
+        <v>275.25</v>
+      </c>
+      <c r="S442" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29344,7 +29542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34517,6 +34715,46 @@
       </c>
       <c r="B517" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -34685,28 +34923,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6212947181686719</v>
+        <v>-0.6216593093732067</v>
       </c>
       <c r="J2" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K2" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07105336159333064</v>
+        <v>0.07221866625865236</v>
       </c>
       <c r="M2" t="n">
-        <v>14.63273700037647</v>
+        <v>14.53103733724229</v>
       </c>
       <c r="N2" t="n">
-        <v>308.6817478677704</v>
+        <v>305.8284418924033</v>
       </c>
       <c r="O2" t="n">
-        <v>17.56934113357045</v>
+        <v>17.48795133491637</v>
       </c>
       <c r="P2" t="n">
-        <v>310.1804308273059</v>
+        <v>310.1837446948378</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34763,28 +35001,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6225383337387537</v>
+        <v>-0.5741912044950116</v>
       </c>
       <c r="J3" t="n">
+        <v>441</v>
+      </c>
+      <c r="K3" t="n">
         <v>438</v>
       </c>
-      <c r="K3" t="n">
-        <v>435</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.08950001439075916</v>
+        <v>0.07557890473324214</v>
       </c>
       <c r="M3" t="n">
-        <v>13.00149676867587</v>
+        <v>13.17352308640119</v>
       </c>
       <c r="N3" t="n">
-        <v>247.7005192909274</v>
+        <v>255.1322926750469</v>
       </c>
       <c r="O3" t="n">
-        <v>15.73850435368391</v>
+        <v>15.97286112989927</v>
       </c>
       <c r="P3" t="n">
-        <v>303.5662359245544</v>
+        <v>303.0909730012876</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34841,28 +35079,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8895751183034778</v>
+        <v>-0.8729599288125008</v>
       </c>
       <c r="J4" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K4" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1253318874210326</v>
+        <v>0.1224373713522473</v>
       </c>
       <c r="M4" t="n">
-        <v>11.25629681608271</v>
+        <v>11.26151547695268</v>
       </c>
       <c r="N4" t="n">
-        <v>346.2364009011295</v>
+        <v>344.8523015806113</v>
       </c>
       <c r="O4" t="n">
-        <v>18.60742864828801</v>
+        <v>18.5701992875847</v>
       </c>
       <c r="P4" t="n">
-        <v>302.8136303792018</v>
+        <v>302.6498701138739</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34919,28 +35157,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.109131770945712</v>
+        <v>-1.08407278624443</v>
       </c>
       <c r="J5" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K5" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L5" t="n">
-        <v>0.264962808274218</v>
+        <v>0.2564128625460923</v>
       </c>
       <c r="M5" t="n">
-        <v>11.40467564932599</v>
+        <v>11.44309871993128</v>
       </c>
       <c r="N5" t="n">
-        <v>210.3898269526464</v>
+        <v>211.5989124636797</v>
       </c>
       <c r="O5" t="n">
-        <v>14.5048208176677</v>
+        <v>14.54643985529379</v>
       </c>
       <c r="P5" t="n">
-        <v>303.1591292995604</v>
+        <v>302.9086541611646</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34997,28 +35235,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.142659597858418</v>
+        <v>-1.109934156881624</v>
       </c>
       <c r="J6" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K6" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2515642733437593</v>
+        <v>0.2397110927962063</v>
       </c>
       <c r="M6" t="n">
-        <v>12.55613861265202</v>
+        <v>12.6576358445811</v>
       </c>
       <c r="N6" t="n">
-        <v>243.5370534463835</v>
+        <v>246.6978377509292</v>
       </c>
       <c r="O6" t="n">
-        <v>15.60567375816833</v>
+        <v>15.70661764196637</v>
       </c>
       <c r="P6" t="n">
-        <v>302.8418826844011</v>
+        <v>302.5196747020146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35075,28 +35313,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.205393039329855</v>
+        <v>-1.166250336954299</v>
       </c>
       <c r="J7" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K7" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2330476608705602</v>
+        <v>0.2199207153024199</v>
       </c>
       <c r="M7" t="n">
-        <v>13.81818764184136</v>
+        <v>13.96073805988229</v>
       </c>
       <c r="N7" t="n">
-        <v>300.4687481404522</v>
+        <v>305.2966719673836</v>
       </c>
       <c r="O7" t="n">
-        <v>17.33403438731019</v>
+        <v>17.47274082585167</v>
       </c>
       <c r="P7" t="n">
-        <v>300.1199908265161</v>
+        <v>299.735072769977</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35153,28 +35391,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.327085773674596</v>
+        <v>-1.278356595486755</v>
       </c>
       <c r="J8" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K8" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2139392653616337</v>
+        <v>0.1996398484760197</v>
       </c>
       <c r="M8" t="n">
-        <v>15.44395478779711</v>
+        <v>15.62097325328518</v>
       </c>
       <c r="N8" t="n">
-        <v>406.6136097680793</v>
+        <v>414.5798202875987</v>
       </c>
       <c r="O8" t="n">
-        <v>20.16466240153996</v>
+        <v>20.36123327030067</v>
       </c>
       <c r="P8" t="n">
-        <v>300.4165627993847</v>
+        <v>299.9374411452902</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35231,28 +35469,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9170629077532438</v>
+        <v>-0.867264999267659</v>
       </c>
       <c r="J9" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K9" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1162149853333287</v>
+        <v>0.1039211689082572</v>
       </c>
       <c r="M9" t="n">
-        <v>15.98457917016552</v>
+        <v>16.1853752391174</v>
       </c>
       <c r="N9" t="n">
-        <v>401.8843353738933</v>
+        <v>410.4041406431399</v>
       </c>
       <c r="O9" t="n">
-        <v>20.0470530346456</v>
+        <v>20.25843381515807</v>
       </c>
       <c r="P9" t="n">
-        <v>291.0925381140324</v>
+        <v>290.6029373335102</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35309,28 +35547,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9279826885683942</v>
+        <v>-0.8745574042355245</v>
       </c>
       <c r="J10" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K10" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1510253538246586</v>
+        <v>0.133107779169596</v>
       </c>
       <c r="M10" t="n">
-        <v>13.73212927827176</v>
+        <v>13.93176927951886</v>
       </c>
       <c r="N10" t="n">
-        <v>306.6665245295922</v>
+        <v>317.7597281903617</v>
       </c>
       <c r="O10" t="n">
-        <v>17.51189665711833</v>
+        <v>17.82581634008276</v>
       </c>
       <c r="P10" t="n">
-        <v>291.5133678009057</v>
+        <v>290.9903918697347</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35387,28 +35625,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9920514341898783</v>
+        <v>-0.9308247973448069</v>
       </c>
       <c r="J11" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K11" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1549487251467896</v>
+        <v>0.1347599876649784</v>
       </c>
       <c r="M11" t="n">
-        <v>14.36141364300713</v>
+        <v>14.56896723615208</v>
       </c>
       <c r="N11" t="n">
-        <v>337.1001063204696</v>
+        <v>351.8575540386641</v>
       </c>
       <c r="O11" t="n">
-        <v>18.3602861176091</v>
+        <v>18.7578664575336</v>
       </c>
       <c r="P11" t="n">
-        <v>285.6524879673867</v>
+        <v>285.0507654294078</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35465,28 +35703,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7127212580115876</v>
+        <v>-0.6593249962607864</v>
       </c>
       <c r="J12" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K12" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06437368340753802</v>
+        <v>0.05489006222297788</v>
       </c>
       <c r="M12" t="n">
-        <v>17.15245917019459</v>
+        <v>17.30607617600813</v>
       </c>
       <c r="N12" t="n">
-        <v>455.001007574525</v>
+        <v>464.5239699698806</v>
       </c>
       <c r="O12" t="n">
-        <v>21.33075262559962</v>
+        <v>21.55281814449982</v>
       </c>
       <c r="P12" t="n">
-        <v>276.2958717599552</v>
+        <v>275.7614330528284</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35543,28 +35781,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.53320169543315</v>
+        <v>-0.4768670324700542</v>
       </c>
       <c r="J13" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K13" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03533160825308945</v>
+        <v>0.02803937039431581</v>
       </c>
       <c r="M13" t="n">
-        <v>17.9676316955228</v>
+        <v>18.14472595977682</v>
       </c>
       <c r="N13" t="n">
-        <v>492.1742637208499</v>
+        <v>503.3231062681454</v>
       </c>
       <c r="O13" t="n">
-        <v>22.18500087268085</v>
+        <v>22.43486363382103</v>
       </c>
       <c r="P13" t="n">
-        <v>274.249686155694</v>
+        <v>273.6992941849607</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35621,28 +35859,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.37319632624322</v>
+        <v>-1.336429182336359</v>
       </c>
       <c r="J14" t="n">
+        <v>441</v>
+      </c>
+      <c r="K14" t="n">
         <v>438</v>
       </c>
-      <c r="K14" t="n">
-        <v>435</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.21440485812445</v>
+        <v>0.2053416345007607</v>
       </c>
       <c r="M14" t="n">
-        <v>16.45263404564151</v>
+        <v>16.54290242457587</v>
       </c>
       <c r="N14" t="n">
-        <v>435.8009914101741</v>
+        <v>439.0087970354311</v>
       </c>
       <c r="O14" t="n">
-        <v>20.87584708245809</v>
+        <v>20.95253676850207</v>
       </c>
       <c r="P14" t="n">
-        <v>284.2807135219861</v>
+        <v>283.9196776491305</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35699,28 +35937,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3648452509875413</v>
+        <v>-0.3319819056031241</v>
       </c>
       <c r="J15" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K15" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02922178534266129</v>
+        <v>0.02423167699277839</v>
       </c>
       <c r="M15" t="n">
-        <v>13.16024206158784</v>
+        <v>13.28236988837188</v>
       </c>
       <c r="N15" t="n">
-        <v>274.483183547675</v>
+        <v>277.4050690384926</v>
       </c>
       <c r="O15" t="n">
-        <v>16.56753402132239</v>
+        <v>16.65548165135108</v>
       </c>
       <c r="P15" t="n">
-        <v>266.9587295447939</v>
+        <v>266.6312303571757</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35777,28 +36015,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.936521176560532</v>
+        <v>-0.9097758439407381</v>
       </c>
       <c r="J16" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K16" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2016275732509787</v>
+        <v>0.1923849646238753</v>
       </c>
       <c r="M16" t="n">
-        <v>11.27876639206772</v>
+        <v>11.38019977262407</v>
       </c>
       <c r="N16" t="n">
-        <v>217.5528876655366</v>
+        <v>219.198378549801</v>
       </c>
       <c r="O16" t="n">
-        <v>14.74967415455462</v>
+        <v>14.80534965982908</v>
       </c>
       <c r="P16" t="n">
-        <v>280.7990134165689</v>
+        <v>280.5351715504186</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35855,28 +36093,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7192741267415308</v>
+        <v>-0.7034351707383535</v>
       </c>
       <c r="J17" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K17" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1527989218283309</v>
+        <v>0.1482003140571012</v>
       </c>
       <c r="M17" t="n">
-        <v>9.604307520112028</v>
+        <v>9.643684571632573</v>
       </c>
       <c r="N17" t="n">
-        <v>177.3520270095143</v>
+        <v>177.0807667965962</v>
       </c>
       <c r="O17" t="n">
-        <v>13.31735810923151</v>
+        <v>13.30716975155109</v>
       </c>
       <c r="P17" t="n">
-        <v>279.1116659091807</v>
+        <v>278.9535263587043</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35933,28 +36171,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8637596789857414</v>
+        <v>-0.8489071573566883</v>
       </c>
       <c r="J18" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K18" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3460812030159739</v>
+        <v>0.3391110662327353</v>
       </c>
       <c r="M18" t="n">
-        <v>6.762993679734921</v>
+        <v>6.792740742603686</v>
       </c>
       <c r="N18" t="n">
-        <v>87.81900766477007</v>
+        <v>88.1102029584582</v>
       </c>
       <c r="O18" t="n">
-        <v>9.371179630375787</v>
+        <v>9.386703519258409</v>
       </c>
       <c r="P18" t="n">
-        <v>284.9039328355216</v>
+        <v>284.756814155835</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36011,28 +36249,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.153124311321079</v>
+        <v>-1.137476349117519</v>
       </c>
       <c r="J19" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K19" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4408149264945579</v>
+        <v>0.4348801408627535</v>
       </c>
       <c r="M19" t="n">
-        <v>8.286440797518342</v>
+        <v>8.295865671351846</v>
       </c>
       <c r="N19" t="n">
-        <v>105.0771771323413</v>
+        <v>105.4811941927185</v>
       </c>
       <c r="O19" t="n">
-        <v>10.25071593267228</v>
+        <v>10.27040379891261</v>
       </c>
       <c r="P19" t="n">
-        <v>294.3470502246007</v>
+        <v>294.1921938023476</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36070,7 +36308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T439"/>
+  <dimension ref="A1:T442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80332,7 +80570,7 @@
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
         <is>
-          <t>2026-03-29 22:11:43+00:00</t>
+          <t>2026-04-14 22:11:35+00:00</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -80342,27 +80580,27 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>-35.39644047938432,173.23894059582597</t>
+          <t>-35.39648478600642,173.23887996057954</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>-35.395892653650726,173.23834448742033</t>
+          <t>-35.3958487074037,173.23840462943812</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>-35.39532273112271,173.23777861424736</t>
+          <t>-35.39531018368132,173.23779578588568</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>-35.394780301268874,173.2371751112621</t>
+          <t>-35.394768714447984,173.2371909682765</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>-35.39426056092402,173.2365405516534</t>
+          <t>-35.39424032910833,173.23656823973522</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -80372,12 +80610,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>-35.39319921582439,173.23530133933318</t>
+          <t>-35.39320479903304,173.2352936984488</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>-35.39265887198814,173.23469496109888</t>
+          <t>-35.39268474674011,173.23465955021723</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -80434,17 +80672,17 @@
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
         <is>
-          <t>2026-04-14 22:11:35+00:00</t>
+          <t>2026-04-21 22:17:21+00:00</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>-35.39703891204475,173.23946744178136</t>
+          <t>-35.397028465726905,173.2394817379506</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>-35.39642282877026,173.23896475131215</t>
+          <t>-35.39648478600642,173.23887996057954</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -80514,17 +80752,17 @@
       </c>
       <c r="Q438" t="inlineStr">
         <is>
-          <t>-35.388642353106924,173.2307705661316</t>
+          <t>-35.38862320270342,173.2307967743908</t>
         </is>
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>-35.388087392339536,173.2301841515888</t>
+          <t>-35.388073644929285,173.23020296560566</t>
         </is>
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>-35.387506674158004,173.22963298232008</t>
+          <t>-35.387513637884176,173.22962345211172</t>
         </is>
       </c>
       <c r="T438" t="inlineStr">
@@ -80536,102 +80774,408 @@
     <row r="439">
       <c r="A439" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21 22:17:21+00:00</t>
+          <t>2026-04-22 22:11:20+00:00</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>-35.397028465726905,173.2394817379506</t>
+          <t>-35.396970290512,173.2395613527566</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>-35.39642282877026,173.23896475131215</t>
+          <t>-35.39648586665535,173.23887848167024</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>-35.3958487074037,173.23840462943812</t>
+          <t>-35.39585152908985,173.23840076786243</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>-35.39531018368132,173.23779578588568</t>
+          <t>-35.39529739609501,173.23781328616232</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>-35.394768714447984,173.2371909682765</t>
+          <t>-35.39476589278663,173.23719482982855</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>-35.39424032910833,173.23656823973522</t>
+          <t>-35.39424693296578,173.23655920208392</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>-35.39373373252479,173.23591568716975</t>
+          <t>-35.39372712869925,173.2359247247997</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>-35.39320479903304,173.2352936984488</t>
+          <t>-35.39319825527233,173.2353026538938</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>-35.39268474674011,173.23465955021723</t>
+          <t>-35.39267400061467,173.23467425682745</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>-35.39207650059296,173.23414609456944</t>
+          <t>-35.39209084872065,173.23412645845562</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>-35.39147143300222,173.23362828382562</t>
+          <t>-35.39149298513615,173.23359878870923</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>-35.390955211828235,173.2329888774538</t>
+          <t>-35.390953050621405,173.2329918351733</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>-35.390253303606734,173.2326035875197</t>
+          <t>-35.39025942701405,173.23259520737255</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>-35.38975178346456,173.2319440522611</t>
+          <t>-35.389761808992624,173.23193033185194</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>-35.38921976252081,173.23132625355603</t>
+          <t>-35.38919869099258,173.2313550909701</t>
         </is>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
-          <t>-35.38862320270342,173.2307967743908</t>
+          <t>-35.388608134513575,173.23081739592772</t>
         </is>
       </c>
       <c r="R439" t="inlineStr">
         <is>
-          <t>-35.388073644929285,173.23020296560566</t>
+          <t>-35.388061758519804,173.23021923274172</t>
         </is>
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>-35.387513637884176,173.22962345211172</t>
+          <t>-35.38751784013239,173.22961770112312</t>
         </is>
       </c>
       <c r="T439" t="inlineStr">
         <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-35.39693757068281,173.2396061308996</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-35.39648586665535,173.23887848167024</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-35.395835319401705,173.23842295137865</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-35.395283407793436,173.23783242965112</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-35.39475682744821,173.2372072360897</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-35.394220637602096,173.23659518835942</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-35.39370353502612,173.2359570137746</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-35.39317069942857,173.23534036533908</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-35.39264440373481,173.23471476160523</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-35.39209084872065,173.23412645845562</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-35.39147203334032,173.23362746223486</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-35.390940683714284,173.23300875989833</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>-35.39024105679038,173.2326203478102</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-35.38973965677586,173.23196064820064</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>-35.38918212192278,173.23137776653303</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>-35.388598229127915,173.23083095191396</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>-35.388050832626334,173.23023418535752</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>-35.387502111716294,173.22963922624882</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-35.39693757068281,173.2396061308996</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-35.39648586665535,173.23887848167024</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-35.395819770104424,173.23844423111362</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-35.395274402447484,173.23784475378207</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-35.394749983417064,173.2372166024042</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-35.394210911916915,173.23660849834584</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-35.39369410956142,173.23596991292726</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-35.39317069942857,173.23534036533908</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-35.39264440373481,173.23471476160523</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-35.39209084872065,173.23412645845562</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-35.39147203334032,173.23362746223486</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-35.39096349645372,173.2329775395277</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-35.39024105679038,173.2326203478102</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-35.3897315523044,173.23197173954355</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>-35.38916585301314,173.23140003129777</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>-35.38859216583047,173.23083924981904</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>-35.38804627016476,173.23024042930578</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>-35.387494067410394,173.2296502352793</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-35.396903830217646,173.2396523057541</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-35.396532034362494,173.23881529934252</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-35.39580644213235,173.23846247087997</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-35.395267738490666,173.23785387363716</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-35.39476565264521,173.23719515847128</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-35.394215834794785,173.23660176119262</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-35.39369158809928,173.2359733636555</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-35.39314716588819,173.23537257204322</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-35.392599317995106,173.23477646355266</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-35.39204570313654,173.23418824235506</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-35.39147389438836,173.2336249153034</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-35.390999216384785,173.23292865496467</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-35.39026278888447,173.2325906065069</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-35.389735034225595,173.23196697437427</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-35.389138297913256,173.2314377417091</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>-35.38858069959315,173.23085494189354</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>-35.388047170650644,173.23023919694762</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>-35.387513878012655,173.2296231234838</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0069/nzd0069.xlsx
+++ b/data/nzd0069/nzd0069.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T442"/>
+  <dimension ref="A1:T443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29478,7 +29478,7 @@
         <v>322.44</v>
       </c>
       <c r="D442" t="n">
-        <v>292.65</v>
+        <v>295.46</v>
       </c>
       <c r="E442" t="n">
         <v>293.99</v>
@@ -29526,6 +29526,72 @@
         <v>277.5</v>
       </c>
       <c r="T442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>292.81</v>
+      </c>
+      <c r="C443" t="n">
+        <v>323.47</v>
+      </c>
+      <c r="D443" t="n">
+        <v>297.86</v>
+      </c>
+      <c r="E443" t="n">
+        <v>295.36</v>
+      </c>
+      <c r="F443" t="n">
+        <v>300.68</v>
+      </c>
+      <c r="G443" t="n">
+        <v>300.21</v>
+      </c>
+      <c r="H443" t="n">
+        <v>303.41</v>
+      </c>
+      <c r="I443" t="n">
+        <v>304.01</v>
+      </c>
+      <c r="J443" t="n">
+        <v>300.27</v>
+      </c>
+      <c r="K443" t="n">
+        <v>299.23</v>
+      </c>
+      <c r="L443" t="n">
+        <v>297.97</v>
+      </c>
+      <c r="M443" t="n">
+        <v>307.23</v>
+      </c>
+      <c r="N443" t="n">
+        <v>279.24</v>
+      </c>
+      <c r="O443" t="n">
+        <v>283.16</v>
+      </c>
+      <c r="P443" t="n">
+        <v>274.84</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="R443" t="n">
+        <v>275.25</v>
+      </c>
+      <c r="S443" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="T443" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29542,7 +29608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B521"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34755,6 +34821,16 @@
       </c>
       <c r="B521" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -34923,28 +34999,28 @@
         <v>0.0289</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6216593093732067</v>
+        <v>-0.6219595478209763</v>
       </c>
       <c r="J2" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07221866625865236</v>
+        <v>0.07259439122329536</v>
       </c>
       <c r="M2" t="n">
-        <v>14.53103733724229</v>
+        <v>14.4995117250113</v>
       </c>
       <c r="N2" t="n">
-        <v>305.8284418924033</v>
+        <v>305.1298043493712</v>
       </c>
       <c r="O2" t="n">
-        <v>17.48795133491637</v>
+        <v>17.46796508896704</v>
       </c>
       <c r="P2" t="n">
-        <v>310.1837446948378</v>
+        <v>310.1867763299527</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35001,28 +35077,28 @@
         <v>0.032</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5741912044950116</v>
+        <v>-0.559682607151997</v>
       </c>
       <c r="J3" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K3" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07557890473324214</v>
+        <v>0.07163313378163461</v>
       </c>
       <c r="M3" t="n">
-        <v>13.17352308640119</v>
+        <v>13.22236414355283</v>
       </c>
       <c r="N3" t="n">
-        <v>255.1322926750469</v>
+        <v>257.4434183205068</v>
       </c>
       <c r="O3" t="n">
-        <v>15.97286112989927</v>
+        <v>16.04504341909073</v>
       </c>
       <c r="P3" t="n">
-        <v>303.0909730012876</v>
+        <v>302.9476705673875</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35079,28 +35155,28 @@
         <v>0.0438</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8729599288125008</v>
+        <v>-0.8643087705231584</v>
       </c>
       <c r="J4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1224373713522473</v>
+        <v>0.1205041129358758</v>
       </c>
       <c r="M4" t="n">
-        <v>11.26151547695268</v>
+        <v>11.27891000119174</v>
       </c>
       <c r="N4" t="n">
-        <v>344.8523015806113</v>
+        <v>345.0346924773353</v>
       </c>
       <c r="O4" t="n">
-        <v>18.5701992875847</v>
+        <v>18.57510948762713</v>
       </c>
       <c r="P4" t="n">
-        <v>302.6498701138739</v>
+        <v>302.5644340347074</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35157,28 +35233,28 @@
         <v>0.0364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.08407278624443</v>
+        <v>-1.075238456610734</v>
       </c>
       <c r="J5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K5" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2564128625460923</v>
+        <v>0.2532451712142075</v>
       </c>
       <c r="M5" t="n">
-        <v>11.44309871993128</v>
+        <v>11.45884065717409</v>
       </c>
       <c r="N5" t="n">
-        <v>211.5989124636797</v>
+        <v>212.1625634041675</v>
       </c>
       <c r="O5" t="n">
-        <v>14.54643985529379</v>
+        <v>14.56580115902203</v>
       </c>
       <c r="P5" t="n">
-        <v>302.9086541611646</v>
+        <v>302.8200740429963</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35235,28 +35311,28 @@
         <v>0.0367</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.109934156881624</v>
+        <v>-1.098652424047525</v>
       </c>
       <c r="J6" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K6" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2397110927962063</v>
+        <v>0.2355600071243954</v>
       </c>
       <c r="M6" t="n">
-        <v>12.6576358445811</v>
+        <v>12.69306760606248</v>
       </c>
       <c r="N6" t="n">
-        <v>246.6978377509292</v>
+        <v>247.8879748237153</v>
       </c>
       <c r="O6" t="n">
-        <v>15.70661764196637</v>
+        <v>15.74445854336424</v>
       </c>
       <c r="P6" t="n">
-        <v>302.5196747020146</v>
+        <v>302.4082096817797</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35313,28 +35389,28 @@
         <v>0.0317</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.166250336954299</v>
+        <v>-1.153423353475387</v>
       </c>
       <c r="J7" t="n">
+        <v>442</v>
+      </c>
+      <c r="K7" t="n">
         <v>441</v>
       </c>
-      <c r="K7" t="n">
-        <v>440</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.2199207153024199</v>
+        <v>0.2156734036270223</v>
       </c>
       <c r="M7" t="n">
-        <v>13.96073805988229</v>
+        <v>14.00771578523943</v>
       </c>
       <c r="N7" t="n">
-        <v>305.2966719673836</v>
+        <v>306.8696622311181</v>
       </c>
       <c r="O7" t="n">
-        <v>17.47274082585167</v>
+        <v>17.5176956883923</v>
       </c>
       <c r="P7" t="n">
-        <v>299.735072769977</v>
+        <v>299.6085003556611</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35391,28 +35467,28 @@
         <v>0.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.278356595486755</v>
+        <v>-1.263104063481344</v>
       </c>
       <c r="J8" t="n">
+        <v>442</v>
+      </c>
+      <c r="K8" t="n">
         <v>441</v>
       </c>
-      <c r="K8" t="n">
-        <v>440</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1996398484760197</v>
+        <v>0.195341230302593</v>
       </c>
       <c r="M8" t="n">
-        <v>15.62097325328518</v>
+        <v>15.67528595389745</v>
       </c>
       <c r="N8" t="n">
-        <v>414.5798202875987</v>
+        <v>416.842718359798</v>
       </c>
       <c r="O8" t="n">
-        <v>20.36123327030067</v>
+        <v>20.41672643593478</v>
       </c>
       <c r="P8" t="n">
-        <v>299.9374411452902</v>
+        <v>299.786934223415</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35469,28 +35545,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.867264999267659</v>
+        <v>-0.8524452695718405</v>
       </c>
       <c r="J9" t="n">
+        <v>442</v>
+      </c>
+      <c r="K9" t="n">
         <v>441</v>
       </c>
-      <c r="K9" t="n">
-        <v>440</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1039211689082572</v>
+        <v>0.1005048121935331</v>
       </c>
       <c r="M9" t="n">
-        <v>16.1853752391174</v>
+        <v>16.24361205894397</v>
       </c>
       <c r="N9" t="n">
-        <v>410.4041406431399</v>
+        <v>412.4973118626701</v>
       </c>
       <c r="O9" t="n">
-        <v>20.25843381515807</v>
+        <v>20.31002983411571</v>
       </c>
       <c r="P9" t="n">
-        <v>290.6029373335102</v>
+        <v>290.4567011611323</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35547,28 +35623,28 @@
         <v>0.0292</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8745574042355245</v>
+        <v>-0.8613262191404294</v>
       </c>
       <c r="J10" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K10" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.133107779169596</v>
+        <v>0.1292859566919495</v>
       </c>
       <c r="M10" t="n">
-        <v>13.93176927951886</v>
+        <v>13.97584911424569</v>
       </c>
       <c r="N10" t="n">
-        <v>317.7597281903617</v>
+        <v>319.4630567305057</v>
       </c>
       <c r="O10" t="n">
-        <v>17.82581634008276</v>
+        <v>17.87352949840925</v>
       </c>
       <c r="P10" t="n">
-        <v>290.9903918697347</v>
+        <v>290.8603755044201</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35625,28 +35701,28 @@
         <v>0.0333</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9308247973448069</v>
+        <v>-0.9149850993925395</v>
       </c>
       <c r="J11" t="n">
+        <v>442</v>
+      </c>
+      <c r="K11" t="n">
         <v>441</v>
       </c>
-      <c r="K11" t="n">
-        <v>440</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1347599876649784</v>
+        <v>0.1302216955007064</v>
       </c>
       <c r="M11" t="n">
-        <v>14.56896723615208</v>
+        <v>14.61489615276526</v>
       </c>
       <c r="N11" t="n">
-        <v>351.8575540386641</v>
+        <v>354.5054201833169</v>
       </c>
       <c r="O11" t="n">
-        <v>18.7578664575336</v>
+        <v>18.82831432134372</v>
       </c>
       <c r="P11" t="n">
-        <v>285.0507654294078</v>
+        <v>284.8944918547382</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35703,28 +35779,28 @@
         <v>0.0404</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6593249962607864</v>
+        <v>-0.6429388815733483</v>
       </c>
       <c r="J12" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K12" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05489006222297788</v>
+        <v>0.05218053936886646</v>
       </c>
       <c r="M12" t="n">
-        <v>17.30607617600813</v>
+        <v>17.3512992209461</v>
       </c>
       <c r="N12" t="n">
-        <v>464.5239699698806</v>
+        <v>467.0735255822227</v>
       </c>
       <c r="O12" t="n">
-        <v>21.55281814449982</v>
+        <v>21.61188389711139</v>
       </c>
       <c r="P12" t="n">
-        <v>275.7614330528284</v>
+        <v>275.5968012485783</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35781,28 +35857,28 @@
         <v>0.0262</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4768670324700542</v>
+        <v>-0.458060533695699</v>
       </c>
       <c r="J13" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K13" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02803937039431581</v>
+        <v>0.02580021797757237</v>
       </c>
       <c r="M13" t="n">
-        <v>18.14472595977682</v>
+        <v>18.20541248819773</v>
       </c>
       <c r="N13" t="n">
-        <v>503.3231062681454</v>
+        <v>507.052781629311</v>
       </c>
       <c r="O13" t="n">
-        <v>22.43486363382103</v>
+        <v>22.51783252511909</v>
       </c>
       <c r="P13" t="n">
-        <v>273.6992941849607</v>
+        <v>273.5148599815826</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35859,28 +35935,28 @@
         <v>0.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.336429182336359</v>
+        <v>-1.323853432883972</v>
       </c>
       <c r="J14" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K14" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2053416345007607</v>
+        <v>0.2022080532958609</v>
       </c>
       <c r="M14" t="n">
-        <v>16.54290242457587</v>
+        <v>16.57404722895564</v>
       </c>
       <c r="N14" t="n">
-        <v>439.0087970354311</v>
+        <v>440.1996492328807</v>
       </c>
       <c r="O14" t="n">
-        <v>20.95253676850207</v>
+        <v>20.98093537554703</v>
       </c>
       <c r="P14" t="n">
-        <v>283.9196776491305</v>
+        <v>283.7957262265242</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35937,28 +36013,28 @@
         <v>0.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3319819056031241</v>
+        <v>-0.3215044788518018</v>
       </c>
       <c r="J15" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K15" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02423167699277839</v>
+        <v>0.02274477208227899</v>
       </c>
       <c r="M15" t="n">
-        <v>13.28236988837188</v>
+        <v>13.32024001857988</v>
       </c>
       <c r="N15" t="n">
-        <v>277.4050690384926</v>
+        <v>278.2463654748751</v>
       </c>
       <c r="O15" t="n">
-        <v>16.65548165135108</v>
+        <v>16.68071837406516</v>
       </c>
       <c r="P15" t="n">
-        <v>266.6312303571757</v>
+        <v>266.5264299844795</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36015,28 +36091,28 @@
         <v>0.0321</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9097758439407381</v>
+        <v>-0.90216525045133</v>
       </c>
       <c r="J16" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K16" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1923849646238753</v>
+        <v>0.1899438919671074</v>
       </c>
       <c r="M16" t="n">
-        <v>11.38019977262407</v>
+        <v>11.40534827788166</v>
       </c>
       <c r="N16" t="n">
-        <v>219.198378549801</v>
+        <v>219.488530421483</v>
       </c>
       <c r="O16" t="n">
-        <v>14.80534965982908</v>
+        <v>14.81514530544615</v>
       </c>
       <c r="P16" t="n">
-        <v>280.5351715504186</v>
+        <v>280.4598483691184</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36093,28 +36169,28 @@
         <v>0.0339</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7034351707383535</v>
+        <v>-0.6981351196617247</v>
       </c>
       <c r="J17" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K17" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1482003140571012</v>
+        <v>0.1466103423599716</v>
       </c>
       <c r="M17" t="n">
-        <v>9.643684571632573</v>
+        <v>9.65744261320665</v>
       </c>
       <c r="N17" t="n">
-        <v>177.0807667965962</v>
+        <v>177.0553222402708</v>
       </c>
       <c r="O17" t="n">
-        <v>13.30716975155109</v>
+        <v>13.30621367032225</v>
       </c>
       <c r="P17" t="n">
-        <v>278.9535263587043</v>
+        <v>278.9004684788411</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36171,28 +36247,28 @@
         <v>0.0355</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8489071573566883</v>
+        <v>-0.8435240935476738</v>
       </c>
       <c r="J18" t="n">
+        <v>442</v>
+      </c>
+      <c r="K18" t="n">
         <v>441</v>
       </c>
-      <c r="K18" t="n">
-        <v>440</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3391110662327353</v>
+        <v>0.3362945041858008</v>
       </c>
       <c r="M18" t="n">
-        <v>6.792740742603686</v>
+        <v>6.805521614683967</v>
       </c>
       <c r="N18" t="n">
-        <v>88.1102029584582</v>
+        <v>88.30496206284604</v>
       </c>
       <c r="O18" t="n">
-        <v>9.386703519258409</v>
+        <v>9.397071994129131</v>
       </c>
       <c r="P18" t="n">
-        <v>284.756814155835</v>
+        <v>284.7033423228157</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36249,28 +36325,28 @@
         <v>0.0307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.137476349117519</v>
+        <v>-1.131875207116671</v>
       </c>
       <c r="J19" t="n">
+        <v>442</v>
+      </c>
+      <c r="K19" t="n">
         <v>441</v>
       </c>
-      <c r="K19" t="n">
-        <v>440</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.4348801408627535</v>
+        <v>0.4325921197741149</v>
       </c>
       <c r="M19" t="n">
-        <v>8.295865671351846</v>
+        <v>8.300678764384186</v>
       </c>
       <c r="N19" t="n">
-        <v>105.4811941927185</v>
+        <v>105.6691792363389</v>
       </c>
       <c r="O19" t="n">
-        <v>10.27040379891261</v>
+        <v>10.27955150949393</v>
       </c>
       <c r="P19" t="n">
-        <v>294.1921938023476</v>
+        <v>294.1365557232884</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36308,7 +36384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T442"/>
+  <dimension ref="A1:T443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81095,7 +81171,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>-35.39580644213235,173.23846247087997</t>
+          <t>-35.395823312222674,173.23843938360716</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -81174,6 +81250,108 @@
         </is>
       </c>
       <c r="T442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-35.396900888432484,173.23965633167376</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-35.39653821807107,173.23880683668457</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-35.39583772083726,173.23841966493237</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-35.395275963374196,173.23784261759954</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-35.39476114999385,173.23720132052182</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-35.39421157230298,173.23660759458141</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-35.393684023712304,173.23598371583887</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-35.393140862259834,173.2353811988358</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-35.39257164217919,173.23481433914813</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-35.39201862777768,173.2342252962298</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-35.391464288978526,173.2336380607549</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-35.39097310181529,173.23296439410322</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-35.3902582863794,173.23259676838043</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-35.389735034225595,173.23196697437427</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-35.389138297913256,173.2314377417091</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-35.38858069959315,173.23085494189354</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>-35.388047170650644,173.23023919694762</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>-35.387513878012655,173.2296231234838</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
